--- a/data/Ferry/CL32-June-2026.xlsx
+++ b/data/Ferry/CL32-June-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Ferry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684D51FE-58F8-47FE-A8CF-E14F1744DDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101F7ACC-BB7F-4C93-B050-FAE3D63369F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C5AC1E55-1BE4-439D-8AD9-7FF9B9368B4A}"/>
   </bookViews>
@@ -960,7 +960,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -986,18 +993,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1476,8 +1487,8 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5" s="3">
-        <v>1</v>
+      <c r="J5" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1502,7 +1513,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1534,7 +1545,7 @@
       <c r="I7">
         <v>9</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1563,6 +1574,7 @@
       <c r="I8">
         <v>73</v>
       </c>
+      <c r="J8" s="5"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1586,7 +1598,7 @@
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1612,7 +1624,7 @@
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1638,7 +1650,7 @@
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1664,7 +1676,7 @@
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1710,8 +1722,8 @@
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14" s="3">
-        <v>1</v>
+      <c r="J14" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1721,6 +1733,7 @@
       <c r="B15" t="s">
         <v>37</v>
       </c>
+      <c r="J15" s="5"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1741,6 +1754,7 @@
       <c r="I16" s="3">
         <v>1</v>
       </c>
+      <c r="J16" s="5"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1761,8 +1775,8 @@
       <c r="I17">
         <v>0</v>
       </c>
-      <c r="J17" s="3">
-        <v>1</v>
+      <c r="J17" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1790,6 +1804,7 @@
       <c r="I18">
         <v>0</v>
       </c>
+      <c r="J18" s="5"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -1810,8 +1825,8 @@
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" s="3">
-        <v>1</v>
+      <c r="J19" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1833,8 +1848,8 @@
       <c r="I20">
         <v>0</v>
       </c>
-      <c r="J20" s="3">
-        <v>1</v>
+      <c r="J20" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1856,8 +1871,8 @@
       <c r="I21">
         <v>0</v>
       </c>
-      <c r="J21" s="3">
-        <v>1</v>
+      <c r="J21" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1879,8 +1894,8 @@
       <c r="I22">
         <v>0</v>
       </c>
-      <c r="J22" s="3">
-        <v>1</v>
+      <c r="J22" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1902,8 +1917,8 @@
       <c r="I23">
         <v>0</v>
       </c>
-      <c r="J23" s="3">
-        <v>1</v>
+      <c r="J23" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1925,8 +1940,8 @@
       <c r="I24">
         <v>0</v>
       </c>
-      <c r="J24" s="3">
-        <v>1</v>
+      <c r="J24" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1948,8 +1963,8 @@
       <c r="I25">
         <v>0</v>
       </c>
-      <c r="J25" s="3">
-        <v>1</v>
+      <c r="J25" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1971,8 +1986,8 @@
       <c r="I26">
         <v>0</v>
       </c>
-      <c r="J26" s="3">
-        <v>1</v>
+      <c r="J26" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1994,8 +2009,8 @@
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27" s="3">
-        <v>1</v>
+      <c r="J27" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2017,8 +2032,8 @@
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28" s="3">
-        <v>1</v>
+      <c r="J28" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2040,8 +2055,8 @@
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" s="3">
-        <v>1</v>
+      <c r="J29" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2066,7 +2081,7 @@
       <c r="I30">
         <v>0</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J30" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2100,8 +2115,8 @@
       <c r="I32">
         <v>0</v>
       </c>
-      <c r="J32" s="3">
-        <v>1</v>
+      <c r="J32" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -2117,8 +2132,8 @@
       <c r="I33">
         <v>0</v>
       </c>
-      <c r="J33" s="3">
-        <v>1</v>
+      <c r="J33" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -2134,8 +2149,8 @@
       <c r="I34">
         <v>0</v>
       </c>
-      <c r="J34" s="3">
-        <v>1</v>
+      <c r="J34" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -2154,7 +2169,7 @@
       <c r="I35">
         <v>0</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="5">
         <v>0</v>
       </c>
       <c r="K35" t="s">
@@ -2177,7 +2192,7 @@
       <c r="I36">
         <v>0</v>
       </c>
-      <c r="J36" s="3">
+      <c r="J36" s="5">
         <v>0</v>
       </c>
       <c r="K36" t="s">
@@ -2200,7 +2215,7 @@
       <c r="I37">
         <v>0</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37" s="5">
         <v>0</v>
       </c>
       <c r="K37" t="s">
@@ -2255,8 +2270,8 @@
       <c r="I39">
         <v>0</v>
       </c>
-      <c r="J39" s="3">
-        <v>1</v>
+      <c r="J39" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2284,8 +2299,8 @@
       <c r="I40">
         <v>0</v>
       </c>
-      <c r="J40" s="3">
-        <v>1</v>
+      <c r="J40" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2313,8 +2328,8 @@
       <c r="I41">
         <v>0</v>
       </c>
-      <c r="J41" s="3">
-        <v>1</v>
+      <c r="J41" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2342,8 +2357,8 @@
       <c r="I42">
         <v>0</v>
       </c>
-      <c r="J42" s="3">
-        <v>1</v>
+      <c r="J42" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2371,8 +2386,8 @@
       <c r="I43">
         <v>0</v>
       </c>
-      <c r="J43" s="3">
-        <v>1</v>
+      <c r="J43" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2449,8 +2464,8 @@
       <c r="I46">
         <v>0</v>
       </c>
-      <c r="J46" s="3">
-        <v>1</v>
+      <c r="J46" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2504,8 +2519,8 @@
       <c r="I48">
         <v>0</v>
       </c>
-      <c r="J48" s="3">
-        <v>1</v>
+      <c r="J48" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2533,8 +2548,8 @@
       <c r="I49">
         <v>0</v>
       </c>
-      <c r="J49" s="3">
-        <v>1</v>
+      <c r="J49" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2562,8 +2577,8 @@
       <c r="I50">
         <v>0</v>
       </c>
-      <c r="J50" s="3">
-        <v>1</v>
+      <c r="J50" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2591,8 +2606,8 @@
       <c r="I51">
         <v>0</v>
       </c>
-      <c r="J51" s="3">
-        <v>1</v>
+      <c r="J51" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2678,8 +2693,8 @@
       <c r="I54">
         <v>0</v>
       </c>
-      <c r="J54" s="3">
-        <v>1</v>
+      <c r="J54" s="5">
+        <v>100</v>
       </c>
       <c r="K54" t="s">
         <v>81</v>
@@ -2768,8 +2783,8 @@
       <c r="I57">
         <v>0</v>
       </c>
-      <c r="J57" s="3">
-        <v>1</v>
+      <c r="J57" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2797,8 +2812,8 @@
       <c r="I58">
         <v>0</v>
       </c>
-      <c r="J58" s="3">
-        <v>1</v>
+      <c r="J58" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2826,8 +2841,8 @@
       <c r="I59">
         <v>0</v>
       </c>
-      <c r="J59" s="3">
-        <v>1</v>
+      <c r="J59" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2855,8 +2870,8 @@
       <c r="I60">
         <v>0</v>
       </c>
-      <c r="J60" s="3">
-        <v>1</v>
+      <c r="J60" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2878,8 +2893,8 @@
       <c r="I61">
         <v>0</v>
       </c>
-      <c r="J61" s="3">
-        <v>1</v>
+      <c r="J61" s="5">
+        <v>100</v>
       </c>
       <c r="K61" t="s">
         <v>144</v>
@@ -3090,8 +3105,8 @@
       <c r="I68">
         <v>0</v>
       </c>
-      <c r="J68" s="3">
-        <v>1</v>
+      <c r="J68" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -3119,8 +3134,8 @@
       <c r="I69">
         <v>0</v>
       </c>
-      <c r="J69" s="3">
-        <v>1</v>
+      <c r="J69" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -3148,8 +3163,8 @@
       <c r="I70">
         <v>0</v>
       </c>
-      <c r="J70" s="3">
-        <v>1</v>
+      <c r="J70" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -3177,8 +3192,8 @@
       <c r="I71">
         <v>0</v>
       </c>
-      <c r="J71" s="3">
-        <v>1</v>
+      <c r="J71" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -3559,7 +3574,7 @@
       <c r="I85">
         <v>0</v>
       </c>
-      <c r="J85" s="3">
+      <c r="J85" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3591,7 +3606,7 @@
       <c r="I86">
         <v>10</v>
       </c>
-      <c r="J86" s="3">
+      <c r="J86" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3704,7 +3719,7 @@
       <c r="I90">
         <v>5</v>
       </c>
-      <c r="J90" s="3">
+      <c r="J90" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3736,7 +3751,7 @@
       <c r="I91">
         <v>10</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3765,6 +3780,7 @@
       <c r="I92">
         <v>33</v>
       </c>
+      <c r="J92" s="5"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
@@ -3791,6 +3807,7 @@
       <c r="I93">
         <v>30</v>
       </c>
+      <c r="J93" s="5"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
@@ -3820,7 +3837,7 @@
       <c r="I94">
         <v>10</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3852,7 +3869,7 @@
       <c r="I95">
         <v>5</v>
       </c>
-      <c r="J95" s="3">
+      <c r="J95" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3884,7 +3901,7 @@
       <c r="I96">
         <v>10</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3916,7 +3933,7 @@
       <c r="I97">
         <v>5</v>
       </c>
-      <c r="J97" s="3">
+      <c r="J97" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3945,6 +3962,7 @@
       <c r="I98">
         <v>17</v>
       </c>
+      <c r="J98" s="5"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
@@ -3974,7 +3992,7 @@
       <c r="I99">
         <v>7</v>
       </c>
-      <c r="J99" s="3">
+      <c r="J99" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4006,7 +4024,7 @@
       <c r="I100">
         <v>5</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4038,7 +4056,7 @@
       <c r="I101">
         <v>5</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4067,6 +4085,7 @@
       <c r="I102">
         <v>15</v>
       </c>
+      <c r="J102" s="5"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
@@ -4096,7 +4115,7 @@
       <c r="I103">
         <v>5</v>
       </c>
-      <c r="J103" s="3">
+      <c r="J103" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4128,7 +4147,7 @@
       <c r="I104">
         <v>5</v>
       </c>
-      <c r="J104" s="3">
+      <c r="J104" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4160,7 +4179,7 @@
       <c r="I105">
         <v>5</v>
       </c>
-      <c r="J105" s="3">
+      <c r="J105" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4189,6 +4208,7 @@
       <c r="I106">
         <v>5</v>
       </c>
+      <c r="J106" s="5"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
@@ -4218,7 +4238,7 @@
       <c r="I107">
         <v>5</v>
       </c>
-      <c r="J107" s="3">
+      <c r="J107" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4247,6 +4267,7 @@
       <c r="I108">
         <v>3</v>
       </c>
+      <c r="J108" s="5"/>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
@@ -4276,7 +4297,7 @@
       <c r="I109">
         <v>3</v>
       </c>
-      <c r="J109" s="3">
+      <c r="J109" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4305,6 +4326,7 @@
       <c r="I110">
         <v>5</v>
       </c>
+      <c r="J110" s="5"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
@@ -4334,7 +4356,7 @@
       <c r="I111">
         <v>5</v>
       </c>
-      <c r="J111" s="3">
+      <c r="J111" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4392,7 +4414,7 @@
       <c r="I113">
         <v>0</v>
       </c>
-      <c r="J113" s="3">
+      <c r="J113" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4424,7 +4446,7 @@
       <c r="I114">
         <v>8</v>
       </c>
-      <c r="J114" s="3">
+      <c r="J114" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4453,6 +4475,7 @@
       <c r="I115">
         <v>22</v>
       </c>
+      <c r="J115" s="5"/>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
@@ -4479,6 +4502,7 @@
       <c r="I116">
         <v>20</v>
       </c>
+      <c r="J116" s="5"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
@@ -4508,7 +4532,7 @@
       <c r="I117">
         <v>10</v>
       </c>
-      <c r="J117" s="3">
+      <c r="J117" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4540,7 +4564,7 @@
       <c r="I118">
         <v>5</v>
       </c>
-      <c r="J118" s="3">
+      <c r="J118" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4572,7 +4596,7 @@
       <c r="I119">
         <v>5</v>
       </c>
-      <c r="J119" s="3">
+      <c r="J119" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4601,6 +4625,7 @@
       <c r="I120">
         <v>22</v>
       </c>
+      <c r="J120" s="5"/>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
@@ -4630,7 +4655,7 @@
       <c r="I121">
         <v>3</v>
       </c>
-      <c r="J121" s="3">
+      <c r="J121" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4662,7 +4687,7 @@
       <c r="I122">
         <v>3</v>
       </c>
-      <c r="J122" s="3">
+      <c r="J122" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4694,7 +4719,7 @@
       <c r="I123">
         <v>3</v>
       </c>
-      <c r="J123" s="3">
+      <c r="J123" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4726,7 +4751,7 @@
       <c r="I124">
         <v>3</v>
       </c>
-      <c r="J124" s="3">
+      <c r="J124" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4758,7 +4783,7 @@
       <c r="I125">
         <v>10</v>
       </c>
-      <c r="J125" s="3">
+      <c r="J125" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4790,7 +4815,7 @@
       <c r="I126">
         <v>3</v>
       </c>
-      <c r="J126" s="3">
+      <c r="J126" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4865,8 +4890,8 @@
       <c r="I129">
         <v>0</v>
       </c>
-      <c r="J129" s="3">
-        <v>1</v>
+      <c r="J129" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -4897,8 +4922,8 @@
       <c r="I130">
         <v>4</v>
       </c>
-      <c r="J130" s="3">
-        <v>0.6</v>
+      <c r="J130" s="5">
+        <v>60</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -4926,8 +4951,8 @@
       <c r="I131">
         <v>0</v>
       </c>
-      <c r="J131" s="3">
-        <v>1</v>
+      <c r="J131" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -4955,8 +4980,8 @@
       <c r="I132">
         <v>0</v>
       </c>
-      <c r="J132" s="3">
-        <v>1</v>
+      <c r="J132" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -4987,7 +5012,7 @@
       <c r="I133">
         <v>10</v>
       </c>
-      <c r="J133" s="3">
+      <c r="J133" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5019,7 +5044,7 @@
       <c r="I134">
         <v>5</v>
       </c>
-      <c r="J134" s="3">
+      <c r="J134" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5051,7 +5076,7 @@
       <c r="I135">
         <v>3</v>
       </c>
-      <c r="J135" s="3">
+      <c r="J135" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5083,7 +5108,7 @@
       <c r="I136">
         <v>5</v>
       </c>
-      <c r="J136" s="3">
+      <c r="J136" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5141,8 +5166,8 @@
       <c r="I138">
         <v>4</v>
       </c>
-      <c r="J138" s="3">
-        <v>0.2</v>
+      <c r="J138" s="5">
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -5173,7 +5198,7 @@
       <c r="I139">
         <v>5</v>
       </c>
-      <c r="J139" s="3">
+      <c r="J139" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5205,7 +5230,7 @@
       <c r="I140">
         <v>5</v>
       </c>
-      <c r="J140" s="3">
+      <c r="J140" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5257,7 +5282,7 @@
       <c r="I142">
         <v>0</v>
       </c>
-      <c r="J142" s="3">
+      <c r="J142" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5289,7 +5314,7 @@
       <c r="I143">
         <v>10</v>
       </c>
-      <c r="J143" s="3">
+      <c r="J143" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5321,7 +5346,7 @@
       <c r="I144">
         <v>10</v>
       </c>
-      <c r="J144" s="3">
+      <c r="J144" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5347,7 +5372,7 @@
       <c r="I145">
         <v>0</v>
       </c>
-      <c r="J145" s="3">
+      <c r="J145" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5393,8 +5418,8 @@
       <c r="I147">
         <v>0</v>
       </c>
-      <c r="J147" s="3">
-        <v>1</v>
+      <c r="J147" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -5416,8 +5441,8 @@
       <c r="I148">
         <v>0</v>
       </c>
-      <c r="J148" s="3">
-        <v>1</v>
+      <c r="J148" s="6">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/Ferry/CL32-June-2026.xlsx
+++ b/data/Ferry/CL32-June-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Ferry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101F7ACC-BB7F-4C93-B050-FAE3D63369F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D554587F-AC6D-4E43-8A06-941647A3A62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C5AC1E55-1BE4-439D-8AD9-7FF9B9368B4A}"/>
   </bookViews>
@@ -1002,7 +1002,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -2639,7 +2639,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="4">
-        <v>0.93330000000000002</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2671,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="4">
-        <v>0.93330000000000002</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2728,7 +2728,7 @@
       <c r="I55">
         <v>10</v>
       </c>
-      <c r="J55" s="3">
+      <c r="J55" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2928,8 +2928,8 @@
       <c r="I62">
         <v>1</v>
       </c>
-      <c r="J62" s="3">
-        <v>0.8</v>
+      <c r="J62" s="5">
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2960,7 +2960,7 @@
       <c r="I63">
         <v>5</v>
       </c>
-      <c r="J63" s="3">
+      <c r="J63" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       <c r="I64">
         <v>10</v>
       </c>
-      <c r="J64" s="3">
+      <c r="J64" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       <c r="I65">
         <v>5</v>
       </c>
-      <c r="J65" s="3">
+      <c r="J65" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       <c r="I72">
         <v>5</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       <c r="I73">
         <v>10</v>
       </c>
-      <c r="J73" s="3">
+      <c r="J73" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3308,8 +3308,8 @@
       <c r="I75">
         <v>0</v>
       </c>
-      <c r="J75" s="3">
-        <v>1</v>
+      <c r="J75" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -3337,8 +3337,8 @@
       <c r="I76">
         <v>0</v>
       </c>
-      <c r="J76" s="3">
-        <v>1</v>
+      <c r="J76" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -3366,8 +3366,8 @@
       <c r="I77">
         <v>0</v>
       </c>
-      <c r="J77" s="3">
-        <v>1</v>
+      <c r="J77" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -3389,8 +3389,8 @@
       <c r="I78">
         <v>0</v>
       </c>
-      <c r="J78" s="3">
-        <v>1</v>
+      <c r="J78" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -3412,8 +3412,8 @@
       <c r="I79">
         <v>0</v>
       </c>
-      <c r="J79" s="3">
-        <v>1</v>
+      <c r="J79" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -3438,6 +3438,7 @@
       <c r="I80">
         <v>0</v>
       </c>
+      <c r="J80" s="5"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
@@ -3464,8 +3465,8 @@
       <c r="I81">
         <v>0</v>
       </c>
-      <c r="J81" s="3">
-        <v>1</v>
+      <c r="J81" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -3493,8 +3494,8 @@
       <c r="I82">
         <v>0</v>
       </c>
-      <c r="J82" s="3">
-        <v>1</v>
+      <c r="J82" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -3522,8 +3523,8 @@
       <c r="I83">
         <v>0</v>
       </c>
-      <c r="J83" s="3">
-        <v>1</v>
+      <c r="J83" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -3687,8 +3688,8 @@
       <c r="I89">
         <v>0</v>
       </c>
-      <c r="J89" s="3">
-        <v>1</v>
+      <c r="J89" s="5">
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">

--- a/data/Ferry/CL32-June-2026.xlsx
+++ b/data/Ferry/CL32-June-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Ferry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D554587F-AC6D-4E43-8A06-941647A3A62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7381D2-92D1-4C26-954B-62063CC27886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C5AC1E55-1BE4-439D-8AD9-7FF9B9368B4A}"/>
   </bookViews>
@@ -1350,8 +1350,8 @@
     <col min="6" max="6" width="16.5703125" customWidth="1"/>
     <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="30.5703125" customWidth="1"/>
     <col min="11" max="11" width="41.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/Ferry/CL32-June-2026.xlsx
+++ b/data/Ferry/CL32-June-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Ferry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7381D2-92D1-4C26-954B-62063CC27886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C7E579-B375-415A-A0CE-822E409C62AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C5AC1E55-1BE4-439D-8AD9-7FF9B9368B4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="297">
   <si>
     <t>Activity ID</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Ferry PS Updated Scope June 26 CL32 Programme</t>
   </si>
   <si>
-    <t>16-Feb-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Key Dates</t>
   </si>
   <si>
@@ -98,9 +95,6 @@
     <t>Contract Completion</t>
   </si>
   <si>
-    <t>14-Sep-26*</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-CD-1020</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
     <t>10-Apr-26 A</t>
   </si>
   <si>
-    <t>11-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-CHA-1010</t>
   </si>
   <si>
@@ -188,9 +179,6 @@
     <t>[GET] - Confirmation whether shaft lining is required</t>
   </si>
   <si>
-    <t>12-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-DEP-1040</t>
   </si>
   <si>
@@ -251,9 +239,6 @@
     <t>[GET] - Catchment Area EPD (Explosion Protection Document)- Confirmation of Hazardous Substances in existing tank</t>
   </si>
   <si>
-    <t>01-Jul-26*</t>
-  </si>
-  <si>
     <t xml:space="preserve">    TQ's / RFI's</t>
   </si>
   <si>
@@ -320,9 +305,6 @@
     <t>Review Information and raise RFI/TQs</t>
   </si>
   <si>
-    <t>23-Feb-26 A</t>
-  </si>
-  <si>
     <t>27-Feb-26 A</t>
   </si>
   <si>
@@ -356,9 +338,6 @@
     <t xml:space="preserve">    JMS001-PS-RFQ-000001 - Optioneering Assessment</t>
   </si>
   <si>
-    <t>29-Apr-26 A</t>
-  </si>
-  <si>
     <t>13-May-26 A</t>
   </si>
   <si>
@@ -408,9 +387,6 @@
   </si>
   <si>
     <t>Civil Modelling - Other Assets</t>
-  </si>
-  <si>
-    <t>01-May-26 A</t>
   </si>
   <si>
     <t xml:space="preserve">      FER-3D-1070</t>
@@ -976,12 +952,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -997,14 +979,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1345,9 +1333,7 @@
   <cols>
     <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="96.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="3" max="6" width="17.7109375" style="7" customWidth="1"/>
     <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
@@ -1362,16 +1348,16 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -1394,16 +1380,16 @@
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="C2" s="8">
+        <v>46069</v>
+      </c>
+      <c r="D2" s="8">
         <v>46328</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="8">
         <v>46069</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="8">
         <v>46302</v>
       </c>
       <c r="G2">
@@ -1418,18 +1404,18 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2">
+      <c r="C3" s="8">
+        <v>46069</v>
+      </c>
+      <c r="D3" s="8">
         <v>46328</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="8">
         <v>46069</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="8">
         <v>46302</v>
       </c>
       <c r="G3">
@@ -1444,18 +1430,18 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2">
+        <v>13</v>
+      </c>
+      <c r="C4" s="8">
+        <v>46069</v>
+      </c>
+      <c r="D4" s="8">
         <v>46328</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="8">
         <v>46069</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="8">
         <v>46302</v>
       </c>
       <c r="G4">
@@ -1470,38 +1456,38 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="C5" s="8">
         <v>46069</v>
       </c>
+      <c r="E5" s="8">
+        <v>46069</v>
+      </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="2">
+      <c r="D6" s="8">
+        <v>46279</v>
+      </c>
+      <c r="F6" s="8">
         <v>46302</v>
       </c>
       <c r="G6">
@@ -1513,27 +1499,27 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2">
+        <v>19</v>
+      </c>
+      <c r="C7" s="8">
         <v>46316</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="8">
         <v>46328</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="8">
         <v>46290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="8">
         <v>46302</v>
       </c>
       <c r="G7">
@@ -1545,24 +1531,24 @@
       <c r="I7">
         <v>9</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="2">
+        <v>20</v>
+      </c>
+      <c r="C8" s="8">
         <v>46211</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="8">
         <v>46315</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="8">
         <v>46185</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="8">
         <v>46289</v>
       </c>
       <c r="G8">
@@ -1574,19 +1560,19 @@
       <c r="I8">
         <v>73</v>
       </c>
-      <c r="J8" s="5"/>
+      <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="2">
+        <v>22</v>
+      </c>
+      <c r="D9" s="8">
         <v>46211</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="8">
         <v>46185</v>
       </c>
       <c r="G9">
@@ -1598,21 +1584,21 @@
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="2">
+        <v>24</v>
+      </c>
+      <c r="D10" s="8">
         <v>46226</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="8">
         <v>46202</v>
       </c>
       <c r="G10">
@@ -1624,21 +1610,21 @@
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="2">
+        <v>26</v>
+      </c>
+      <c r="D11" s="8">
         <v>46315</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="8">
         <v>46289</v>
       </c>
       <c r="G11">
@@ -1650,21 +1636,21 @@
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="2">
+        <v>28</v>
+      </c>
+      <c r="D12" s="8">
         <v>46315</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="8">
         <v>46289</v>
       </c>
       <c r="G12">
@@ -1676,24 +1662,24 @@
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="2">
+        <v>29</v>
+      </c>
+      <c r="C13" s="8">
         <v>46122</v>
       </c>
-      <c r="F13" s="2">
+      <c r="D13" s="8">
+        <v>46153</v>
+      </c>
+      <c r="E13" s="8">
+        <v>46122</v>
+      </c>
+      <c r="F13" s="8">
         <v>46153</v>
       </c>
       <c r="G13">
@@ -1705,94 +1691,94 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="2">
+      <c r="C14" s="8">
         <v>46122</v>
       </c>
+      <c r="E14" s="8">
+        <v>46122</v>
+      </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="2">
+        <v>36</v>
+      </c>
+      <c r="D16" s="8">
         <v>46135</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>0</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <v>1</v>
       </c>
-      <c r="J16" s="5"/>
+      <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="2">
+        <v>38</v>
+      </c>
+      <c r="C17" s="8">
         <v>46153</v>
       </c>
+      <c r="E17" s="8">
+        <v>46153</v>
+      </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2">
+        <v>39</v>
+      </c>
+      <c r="C18" s="8">
+        <v>46069</v>
+      </c>
+      <c r="D18" s="8">
         <v>46204</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="8">
         <v>46069</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="8">
         <v>46174</v>
       </c>
       <c r="G18">
@@ -1804,272 +1790,272 @@
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18" s="5"/>
+      <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="2">
+        <v>41</v>
+      </c>
+      <c r="C19" s="8">
         <v>46069</v>
       </c>
+      <c r="E19" s="8">
+        <v>46069</v>
+      </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="2">
+        <v>43</v>
+      </c>
+      <c r="C20" s="8">
         <v>46069</v>
       </c>
+      <c r="E20" s="8">
+        <v>46069</v>
+      </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="2">
+        <v>45</v>
+      </c>
+      <c r="C21" s="8">
         <v>46093</v>
       </c>
+      <c r="E21" s="8">
+        <v>46093</v>
+      </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="2">
+        <v>47</v>
+      </c>
+      <c r="C22" s="8">
         <v>46094</v>
       </c>
+      <c r="E22" s="8">
+        <v>46094</v>
+      </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="2">
+        <v>50</v>
+      </c>
+      <c r="C23" s="8">
         <v>46094</v>
       </c>
+      <c r="E23" s="8">
+        <v>46094</v>
+      </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J23" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="2">
+        <v>52</v>
+      </c>
+      <c r="C24" s="8">
         <v>46101</v>
       </c>
+      <c r="E24" s="8">
+        <v>46101</v>
+      </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
-      <c r="J24" s="5">
+      <c r="J24" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" s="2">
+        <v>55</v>
+      </c>
+      <c r="C25" s="8">
         <v>46101</v>
       </c>
+      <c r="E25" s="8">
+        <v>46101</v>
+      </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
-      <c r="J25" s="5">
+      <c r="J25" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="2">
+      <c r="C26" s="8">
         <v>46101</v>
       </c>
+      <c r="E26" s="8">
+        <v>46101</v>
+      </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
-      <c r="J26" s="5">
+      <c r="J26" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="2">
+        <v>59</v>
+      </c>
+      <c r="C27" s="8">
         <v>46101</v>
       </c>
+      <c r="E27" s="8">
+        <v>46101</v>
+      </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27" s="5">
+      <c r="J27" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" s="2">
+        <v>61</v>
+      </c>
+      <c r="C28" s="8">
         <v>46101</v>
       </c>
+      <c r="E28" s="8">
+        <v>46101</v>
+      </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28" s="5">
+      <c r="J28" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="2">
+        <v>63</v>
+      </c>
+      <c r="C29" s="8">
         <v>46101</v>
       </c>
+      <c r="E29" s="8">
+        <v>46101</v>
+      </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" s="5">
+      <c r="J29" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" t="s">
-        <v>70</v>
-      </c>
-      <c r="E30" s="2">
+        <v>65</v>
+      </c>
+      <c r="C30" s="8">
+        <v>46204</v>
+      </c>
+      <c r="E30" s="8">
         <v>46174</v>
       </c>
       <c r="G30">
@@ -2081,18 +2067,18 @@
       <c r="I30">
         <v>0</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J30" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="2">
+        <v>66</v>
+      </c>
+      <c r="C31" s="8">
+        <v>46184</v>
+      </c>
+      <c r="D31" s="8">
         <v>46204</v>
       </c>
       <c r="H31">
@@ -2104,63 +2090,63 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="C32" s="8">
+        <v>46184</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J32" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="C33" s="8">
+        <v>46184</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
-      <c r="J33" s="5">
+      <c r="J33" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="C34" s="8">
+        <v>46184</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
-      <c r="J34" s="5">
+      <c r="J34" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="2">
+        <v>75</v>
+      </c>
+      <c r="D35" s="8">
         <v>46204</v>
       </c>
       <c r="H35">
@@ -2169,21 +2155,21 @@
       <c r="I35">
         <v>0</v>
       </c>
-      <c r="J35" s="5">
+      <c r="J35" s="4">
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
-      </c>
-      <c r="D36" s="2">
+        <v>78</v>
+      </c>
+      <c r="D36" s="8">
         <v>46204</v>
       </c>
       <c r="H36">
@@ -2192,21 +2178,21 @@
       <c r="I36">
         <v>0</v>
       </c>
-      <c r="J36" s="5">
+      <c r="J36" s="4">
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="2">
+        <v>80</v>
+      </c>
+      <c r="D37" s="8">
         <v>46204</v>
       </c>
       <c r="H37">
@@ -2215,27 +2201,27 @@
       <c r="I37">
         <v>0</v>
       </c>
-      <c r="J37" s="5">
+      <c r="J37" s="4">
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" t="s">
-        <v>87</v>
-      </c>
-      <c r="E38" s="2">
+        <v>81</v>
+      </c>
+      <c r="C38" s="8">
         <v>46069</v>
       </c>
-      <c r="F38" s="2">
+      <c r="D38" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" s="8">
+        <v>46069</v>
+      </c>
+      <c r="F38" s="8">
         <v>46108</v>
       </c>
       <c r="G38">
@@ -2247,21 +2233,21 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
-      </c>
-      <c r="C39" t="s">
-        <v>12</v>
-      </c>
-      <c r="D39" t="s">
-        <v>90</v>
-      </c>
-      <c r="E39" s="2">
+        <v>84</v>
+      </c>
+      <c r="C39" s="8">
         <v>46069</v>
       </c>
-      <c r="F39" s="2">
+      <c r="D39" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" s="8">
+        <v>46069</v>
+      </c>
+      <c r="F39" s="8">
         <v>46073</v>
       </c>
       <c r="G39">
@@ -2270,27 +2256,27 @@
       <c r="I39">
         <v>0</v>
       </c>
-      <c r="J39" s="5">
+      <c r="J39" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" t="s">
-        <v>93</v>
-      </c>
-      <c r="D40" t="s">
-        <v>94</v>
-      </c>
-      <c r="E40" s="2">
+        <v>87</v>
+      </c>
+      <c r="C40" s="8">
         <v>46076</v>
       </c>
-      <c r="F40" s="2">
+      <c r="D40" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" s="8">
+        <v>46076</v>
+      </c>
+      <c r="F40" s="8">
         <v>46080</v>
       </c>
       <c r="G40">
@@ -2299,56 +2285,56 @@
       <c r="I40">
         <v>0</v>
       </c>
-      <c r="J40" s="5">
+      <c r="J40" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" t="s">
-        <v>97</v>
-      </c>
-      <c r="E41" s="2">
+        <v>90</v>
+      </c>
+      <c r="C41" s="8">
         <v>46090</v>
       </c>
-      <c r="F41" s="2">
+      <c r="D41" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E41" s="8">
         <v>46090</v>
       </c>
+      <c r="F41" s="8">
+        <v>46090</v>
+      </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
-      <c r="J41" s="5">
+      <c r="J41" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
-      </c>
-      <c r="C42" t="s">
-        <v>97</v>
-      </c>
-      <c r="D42" t="s">
-        <v>52</v>
-      </c>
-      <c r="E42" s="2">
+        <v>93</v>
+      </c>
+      <c r="C42" s="8">
         <v>46090</v>
       </c>
-      <c r="F42" s="2">
+      <c r="D42" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" s="8">
+        <v>46090</v>
+      </c>
+      <c r="F42" s="8">
         <v>46094</v>
       </c>
       <c r="G42">
@@ -2357,53 +2343,53 @@
       <c r="I42">
         <v>0</v>
       </c>
-      <c r="J42" s="5">
+      <c r="J42" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="8">
+        <v>46097</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="8">
+        <v>46097</v>
+      </c>
+      <c r="F43" s="8">
+        <v>46108</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4">
         <v>100</v>
       </c>
-      <c r="B43" t="s">
-        <v>101</v>
-      </c>
-      <c r="C43" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" t="s">
-        <v>87</v>
-      </c>
-      <c r="E43" s="2">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="8">
         <v>46097</v>
       </c>
-      <c r="F43" s="2">
-        <v>46108</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43" s="5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" t="s">
-        <v>102</v>
-      </c>
-      <c r="D44" s="2">
+      <c r="D44" s="8">
         <v>46315</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="8">
         <v>46097</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="8">
         <v>46289</v>
       </c>
       <c r="G44">
@@ -2418,18 +2404,18 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>104</v>
-      </c>
-      <c r="C45" t="s">
-        <v>105</v>
-      </c>
-      <c r="D45" t="s">
-        <v>106</v>
-      </c>
-      <c r="E45" s="2">
+        <v>98</v>
+      </c>
+      <c r="C45" s="8">
         <v>46141</v>
       </c>
-      <c r="F45" s="2">
+      <c r="D45" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E45" s="8">
+        <v>46141</v>
+      </c>
+      <c r="F45" s="8">
         <v>46155</v>
       </c>
       <c r="G45">
@@ -2441,21 +2427,21 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>108</v>
-      </c>
-      <c r="C46" t="s">
-        <v>105</v>
-      </c>
-      <c r="D46" t="s">
-        <v>106</v>
-      </c>
-      <c r="E46" s="2">
+        <v>101</v>
+      </c>
+      <c r="C46" s="8">
         <v>46141</v>
       </c>
-      <c r="F46" s="2">
+      <c r="D46" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="8">
+        <v>46141</v>
+      </c>
+      <c r="F46" s="8">
         <v>46155</v>
       </c>
       <c r="G46">
@@ -2464,24 +2450,24 @@
       <c r="I46">
         <v>0</v>
       </c>
-      <c r="J46" s="5">
+      <c r="J46" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D47" s="2">
+        <v>102</v>
+      </c>
+      <c r="C47" s="8">
+        <v>46111</v>
+      </c>
+      <c r="D47" s="8">
         <v>46217</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="8">
         <v>46111</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="8">
         <v>46185</v>
       </c>
       <c r="G47">
@@ -2496,21 +2482,21 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
-      </c>
-      <c r="C48" t="s">
-        <v>110</v>
-      </c>
-      <c r="D48" t="s">
-        <v>39</v>
-      </c>
-      <c r="E48" s="2">
+        <v>105</v>
+      </c>
+      <c r="C48" s="8">
         <v>46111</v>
       </c>
-      <c r="F48" s="2">
+      <c r="D48" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E48" s="8">
+        <v>46111</v>
+      </c>
+      <c r="F48" s="8">
         <v>46135</v>
       </c>
       <c r="G48">
@@ -2519,27 +2505,27 @@
       <c r="I48">
         <v>0</v>
       </c>
-      <c r="J48" s="5">
+      <c r="J48" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
-      </c>
-      <c r="C49" t="s">
-        <v>110</v>
-      </c>
-      <c r="D49" t="s">
-        <v>39</v>
-      </c>
-      <c r="E49" s="2">
+        <v>107</v>
+      </c>
+      <c r="C49" s="8">
         <v>46111</v>
       </c>
-      <c r="F49" s="2">
+      <c r="D49" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="8">
+        <v>46111</v>
+      </c>
+      <c r="F49" s="8">
         <v>46135</v>
       </c>
       <c r="G49">
@@ -2548,27 +2534,27 @@
       <c r="I49">
         <v>0</v>
       </c>
-      <c r="J49" s="5">
+      <c r="J49" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
-      </c>
-      <c r="C50" t="s">
-        <v>32</v>
-      </c>
-      <c r="D50" t="s">
-        <v>39</v>
-      </c>
-      <c r="E50" s="2">
+        <v>109</v>
+      </c>
+      <c r="C50" s="8">
         <v>46122</v>
       </c>
-      <c r="F50" s="2">
+      <c r="D50" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E50" s="8">
+        <v>46122</v>
+      </c>
+      <c r="F50" s="8">
         <v>46135</v>
       </c>
       <c r="G50">
@@ -2577,27 +2563,27 @@
       <c r="I50">
         <v>0</v>
       </c>
-      <c r="J50" s="5">
+      <c r="J50" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>118</v>
-      </c>
-      <c r="C51" t="s">
-        <v>119</v>
-      </c>
-      <c r="D51" t="s">
-        <v>120</v>
-      </c>
-      <c r="E51" s="2">
+        <v>111</v>
+      </c>
+      <c r="C51" s="8">
         <v>46136</v>
       </c>
-      <c r="F51" s="2">
+      <c r="D51" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E51" s="8">
+        <v>46136</v>
+      </c>
+      <c r="F51" s="8">
         <v>46142</v>
       </c>
       <c r="G51">
@@ -2606,27 +2592,27 @@
       <c r="I51">
         <v>0</v>
       </c>
-      <c r="J51" s="5">
+      <c r="J51" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B52" t="s">
-        <v>122</v>
-      </c>
-      <c r="C52" t="s">
-        <v>123</v>
-      </c>
-      <c r="D52" s="2">
+        <v>115</v>
+      </c>
+      <c r="C52" s="8">
+        <v>46143</v>
+      </c>
+      <c r="D52" s="8">
         <v>46204</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="8">
         <v>46143</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="8">
         <v>46178</v>
       </c>
       <c r="G52">
@@ -2638,27 +2624,27 @@
       <c r="I52">
         <v>1</v>
       </c>
-      <c r="J52" s="4">
+      <c r="J52" s="3">
         <v>93.33</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
-      </c>
-      <c r="C53" t="s">
-        <v>123</v>
-      </c>
-      <c r="D53" s="2">
+        <v>117</v>
+      </c>
+      <c r="C53" s="8">
+        <v>46143</v>
+      </c>
+      <c r="D53" s="8">
         <v>46204</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="8">
         <v>46143</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="8">
         <v>46178</v>
       </c>
       <c r="G53">
@@ -2670,21 +2656,21 @@
       <c r="I53">
         <v>1</v>
       </c>
-      <c r="J53" s="4">
+      <c r="J53" s="3">
         <v>93.33</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
-      </c>
-      <c r="D54" t="s">
-        <v>128</v>
-      </c>
-      <c r="F54" s="2">
+        <v>119</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F54" s="8">
         <v>46163</v>
       </c>
       <c r="G54">
@@ -2693,30 +2679,30 @@
       <c r="I54">
         <v>0</v>
       </c>
-      <c r="J54" s="5">
+      <c r="J54" s="4">
         <v>100</v>
       </c>
       <c r="K54" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
-      </c>
-      <c r="C55" s="2">
+        <v>122</v>
+      </c>
+      <c r="C55" s="8">
         <v>46204</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="8">
         <v>46217</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="8">
         <v>46174</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="8">
         <v>46185</v>
       </c>
       <c r="G55">
@@ -2728,24 +2714,24 @@
       <c r="I55">
         <v>10</v>
       </c>
-      <c r="J55" s="5">
+      <c r="J55" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>131</v>
-      </c>
-      <c r="C56" t="s">
-        <v>110</v>
-      </c>
-      <c r="D56" s="2">
+        <v>123</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56" s="8">
         <v>46232</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="8">
         <v>46111</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="8">
         <v>46206</v>
       </c>
       <c r="G56">
@@ -2760,21 +2746,21 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
-      </c>
-      <c r="C57" t="s">
-        <v>110</v>
-      </c>
-      <c r="D57" t="s">
-        <v>134</v>
-      </c>
-      <c r="E57" s="2">
+        <v>125</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E57" s="8">
         <v>46111</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="8">
         <v>46114</v>
       </c>
       <c r="G57">
@@ -2783,27 +2769,27 @@
       <c r="I57">
         <v>0</v>
       </c>
-      <c r="J57" s="5">
+      <c r="J57" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B58" t="s">
-        <v>136</v>
-      </c>
-      <c r="C58" t="s">
-        <v>110</v>
-      </c>
-      <c r="D58" t="s">
-        <v>134</v>
-      </c>
-      <c r="E58" s="2">
+        <v>128</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E58" s="8">
         <v>46111</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="8">
         <v>46114</v>
       </c>
       <c r="G58">
@@ -2812,27 +2798,27 @@
       <c r="I58">
         <v>0</v>
       </c>
-      <c r="J58" s="5">
+      <c r="J58" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
-      </c>
-      <c r="C59" t="s">
-        <v>110</v>
-      </c>
-      <c r="D59" t="s">
-        <v>134</v>
-      </c>
-      <c r="E59" s="2">
+        <v>130</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E59" s="8">
         <v>46111</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="8">
         <v>46114</v>
       </c>
       <c r="G59">
@@ -2841,27 +2827,27 @@
       <c r="I59">
         <v>0</v>
       </c>
-      <c r="J59" s="5">
+      <c r="J59" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
-      </c>
-      <c r="C60" t="s">
-        <v>110</v>
-      </c>
-      <c r="D60" t="s">
-        <v>134</v>
-      </c>
-      <c r="E60" s="2">
+        <v>132</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E60" s="8">
         <v>46111</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="8">
         <v>46114</v>
       </c>
       <c r="G60">
@@ -2870,21 +2856,21 @@
       <c r="I60">
         <v>0</v>
       </c>
-      <c r="J60" s="5">
+      <c r="J60" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
-      </c>
-      <c r="D61" t="s">
-        <v>143</v>
-      </c>
-      <c r="F61" s="2">
+        <v>134</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F61" s="8">
         <v>46174</v>
       </c>
       <c r="G61">
@@ -2893,30 +2879,30 @@
       <c r="I61">
         <v>0</v>
       </c>
-      <c r="J61" s="5">
+      <c r="J61" s="4">
         <v>100</v>
       </c>
       <c r="K61" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B62" t="s">
-        <v>146</v>
-      </c>
-      <c r="C62" t="s">
-        <v>147</v>
-      </c>
-      <c r="D62" s="2">
+        <v>138</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D62" s="8">
         <v>46204</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="8">
         <v>46174</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="8">
         <v>46178</v>
       </c>
       <c r="G62">
@@ -2928,27 +2914,27 @@
       <c r="I62">
         <v>1</v>
       </c>
-      <c r="J62" s="5">
+      <c r="J62" s="4">
         <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B63" t="s">
-        <v>149</v>
-      </c>
-      <c r="C63" s="2">
+        <v>141</v>
+      </c>
+      <c r="C63" s="8">
         <v>46205</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="8">
         <v>46211</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="8">
         <v>46181</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="8">
         <v>46185</v>
       </c>
       <c r="G63">
@@ -2960,27 +2946,27 @@
       <c r="I63">
         <v>5</v>
       </c>
-      <c r="J63" s="5">
+      <c r="J63" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B64" t="s">
-        <v>151</v>
-      </c>
-      <c r="C64" s="2">
+        <v>143</v>
+      </c>
+      <c r="C64" s="8">
         <v>46212</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="8">
         <v>46225</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="8">
         <v>46188</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="8">
         <v>46199</v>
       </c>
       <c r="G64">
@@ -2992,27 +2978,27 @@
       <c r="I64">
         <v>10</v>
       </c>
-      <c r="J64" s="5">
+      <c r="J64" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B65" t="s">
-        <v>153</v>
-      </c>
-      <c r="C65" s="2">
+        <v>145</v>
+      </c>
+      <c r="C65" s="8">
         <v>46226</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="8">
         <v>46232</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="8">
         <v>46202</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="8">
         <v>46206</v>
       </c>
       <c r="G65">
@@ -3024,24 +3010,24 @@
       <c r="I65">
         <v>5</v>
       </c>
-      <c r="J65" s="5">
+      <c r="J65" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>154</v>
-      </c>
-      <c r="C66" t="s">
-        <v>155</v>
-      </c>
-      <c r="D66" s="2">
+        <v>146</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D66" s="8">
         <v>46239</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="8">
         <v>46104</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="8">
         <v>46213</v>
       </c>
       <c r="G66">
@@ -3056,18 +3042,18 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>156</v>
-      </c>
-      <c r="C67" t="s">
-        <v>110</v>
-      </c>
-      <c r="D67" s="2">
+        <v>148</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D67" s="8">
         <v>46225</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="8">
         <v>46111</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="8">
         <v>46199</v>
       </c>
       <c r="G67">
@@ -3082,21 +3068,21 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
-      </c>
-      <c r="C68" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" t="s">
-        <v>134</v>
-      </c>
-      <c r="E68" s="2">
+        <v>150</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E68" s="8">
         <v>46111</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="8">
         <v>46114</v>
       </c>
       <c r="G68">
@@ -3105,27 +3091,27 @@
       <c r="I68">
         <v>0</v>
       </c>
-      <c r="J68" s="5">
+      <c r="J68" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B69" t="s">
-        <v>160</v>
-      </c>
-      <c r="C69" t="s">
-        <v>161</v>
-      </c>
-      <c r="D69" t="s">
-        <v>162</v>
-      </c>
-      <c r="E69" s="2">
+        <v>152</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E69" s="8">
         <v>46119</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="8">
         <v>46125</v>
       </c>
       <c r="G69">
@@ -3134,27 +3120,27 @@
       <c r="I69">
         <v>0</v>
       </c>
-      <c r="J69" s="5">
+      <c r="J69" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B70" t="s">
-        <v>164</v>
-      </c>
-      <c r="C70" t="s">
-        <v>165</v>
-      </c>
-      <c r="D70" t="s">
-        <v>166</v>
-      </c>
-      <c r="E70" s="2">
+        <v>156</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E70" s="8">
         <v>46126</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="8">
         <v>46132</v>
       </c>
       <c r="G70">
@@ -3163,27 +3149,27 @@
       <c r="I70">
         <v>0</v>
       </c>
-      <c r="J70" s="5">
+      <c r="J70" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
-      </c>
-      <c r="C71" t="s">
-        <v>169</v>
-      </c>
-      <c r="D71" t="s">
-        <v>170</v>
-      </c>
-      <c r="E71" s="2">
+        <v>160</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E71" s="8">
         <v>46133</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="8">
         <v>46164</v>
       </c>
       <c r="G71">
@@ -3192,27 +3178,27 @@
       <c r="I71">
         <v>0</v>
       </c>
-      <c r="J71" s="5">
+      <c r="J71" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>172</v>
-      </c>
-      <c r="C72" s="2">
+        <v>164</v>
+      </c>
+      <c r="C72" s="8">
         <v>46204</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="8">
         <v>46210</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="8">
         <v>46168</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="8">
         <v>46174</v>
       </c>
       <c r="G72">
@@ -3224,27 +3210,27 @@
       <c r="I72">
         <v>5</v>
       </c>
-      <c r="J72" s="5">
+      <c r="J72" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B73" t="s">
-        <v>174</v>
-      </c>
-      <c r="C73" s="2">
+        <v>166</v>
+      </c>
+      <c r="C73" s="8">
         <v>46212</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="8">
         <v>46225</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="8">
         <v>46188</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="8">
         <v>46199</v>
       </c>
       <c r="G73">
@@ -3256,24 +3242,24 @@
       <c r="I73">
         <v>10</v>
       </c>
-      <c r="J73" s="5">
+      <c r="J73" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>175</v>
-      </c>
-      <c r="C74" t="s">
-        <v>110</v>
-      </c>
-      <c r="D74" t="s">
-        <v>170</v>
-      </c>
-      <c r="E74" s="2">
+        <v>167</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E74" s="8">
         <v>46111</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="8">
         <v>46164</v>
       </c>
       <c r="G74">
@@ -3285,21 +3271,21 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B75" t="s">
-        <v>177</v>
-      </c>
-      <c r="C75" t="s">
-        <v>110</v>
-      </c>
-      <c r="D75" t="s">
-        <v>32</v>
-      </c>
-      <c r="E75" s="2">
+        <v>169</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E75" s="8">
         <v>46111</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="8">
         <v>46122</v>
       </c>
       <c r="G75">
@@ -3308,27 +3294,27 @@
       <c r="I75">
         <v>0</v>
       </c>
-      <c r="J75" s="5">
+      <c r="J75" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B76" t="s">
-        <v>179</v>
-      </c>
-      <c r="C76" t="s">
-        <v>162</v>
-      </c>
-      <c r="D76" t="s">
-        <v>119</v>
-      </c>
-      <c r="E76" s="2">
+        <v>171</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E76" s="8">
         <v>46125</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="8">
         <v>46136</v>
       </c>
       <c r="G76">
@@ -3337,27 +3323,27 @@
       <c r="I76">
         <v>0</v>
       </c>
-      <c r="J76" s="5">
+      <c r="J76" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B77" t="s">
-        <v>181</v>
-      </c>
-      <c r="C77" t="s">
-        <v>182</v>
-      </c>
-      <c r="D77" t="s">
-        <v>170</v>
-      </c>
-      <c r="E77" s="2">
+        <v>173</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E77" s="8">
         <v>46139</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="8">
         <v>46164</v>
       </c>
       <c r="G77">
@@ -3366,21 +3352,21 @@
       <c r="I77">
         <v>0</v>
       </c>
-      <c r="J77" s="5">
+      <c r="J77" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B78" t="s">
-        <v>184</v>
-      </c>
-      <c r="C78" t="s">
-        <v>120</v>
-      </c>
-      <c r="E78" s="2">
+        <v>176</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" s="8">
         <v>46142</v>
       </c>
       <c r="G78">
@@ -3389,21 +3375,21 @@
       <c r="I78">
         <v>0</v>
       </c>
-      <c r="J78" s="5">
+      <c r="J78" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B79" t="s">
-        <v>186</v>
-      </c>
-      <c r="D79" t="s">
-        <v>187</v>
-      </c>
-      <c r="F79" s="2">
+        <v>178</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F79" s="8">
         <v>46154</v>
       </c>
       <c r="G79">
@@ -3412,24 +3398,24 @@
       <c r="I79">
         <v>0</v>
       </c>
-      <c r="J79" s="5">
+      <c r="J79" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>188</v>
-      </c>
-      <c r="C80" t="s">
-        <v>155</v>
-      </c>
-      <c r="D80" t="s">
-        <v>119</v>
-      </c>
-      <c r="E80" s="2">
+        <v>180</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E80" s="8">
         <v>46104</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="8">
         <v>46136</v>
       </c>
       <c r="G80">
@@ -3438,25 +3424,25 @@
       <c r="I80">
         <v>0</v>
       </c>
-      <c r="J80" s="5"/>
+      <c r="J80" s="4"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B81" t="s">
-        <v>190</v>
-      </c>
-      <c r="C81" t="s">
-        <v>155</v>
-      </c>
-      <c r="D81" t="s">
-        <v>191</v>
-      </c>
-      <c r="E81" s="2">
+        <v>182</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E81" s="8">
         <v>46104</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="8">
         <v>46129</v>
       </c>
       <c r="G81">
@@ -3465,27 +3451,27 @@
       <c r="I81">
         <v>0</v>
       </c>
-      <c r="J81" s="5">
+      <c r="J81" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B82" t="s">
-        <v>193</v>
-      </c>
-      <c r="C82" t="s">
-        <v>110</v>
-      </c>
-      <c r="D82" t="s">
-        <v>191</v>
-      </c>
-      <c r="E82" s="2">
+        <v>185</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E82" s="8">
         <v>46111</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="8">
         <v>46129</v>
       </c>
       <c r="G82">
@@ -3494,27 +3480,27 @@
       <c r="I82">
         <v>0</v>
       </c>
-      <c r="J82" s="5">
+      <c r="J82" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B83" t="s">
-        <v>195</v>
-      </c>
-      <c r="C83" t="s">
-        <v>166</v>
-      </c>
-      <c r="D83" t="s">
-        <v>119</v>
-      </c>
-      <c r="E83" s="2">
+        <v>187</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E83" s="8">
         <v>46132</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="8">
         <v>46136</v>
       </c>
       <c r="G83">
@@ -3523,24 +3509,24 @@
       <c r="I83">
         <v>0</v>
       </c>
-      <c r="J83" s="5">
+      <c r="J83" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>196</v>
-      </c>
-      <c r="C84" s="2">
+        <v>188</v>
+      </c>
+      <c r="C84" s="8">
         <v>46226</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="8">
         <v>46239</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E84" s="8">
         <v>46202</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="8">
         <v>46213</v>
       </c>
       <c r="G84">
@@ -3555,15 +3541,15 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B85" t="s">
-        <v>198</v>
-      </c>
-      <c r="C85" s="2">
+        <v>190</v>
+      </c>
+      <c r="C85" s="8">
         <v>46226</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="8">
         <v>46202</v>
       </c>
       <c r="G85">
@@ -3575,27 +3561,27 @@
       <c r="I85">
         <v>0</v>
       </c>
-      <c r="J85" s="5">
+      <c r="J85" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B86" t="s">
-        <v>200</v>
-      </c>
-      <c r="C86" s="2">
+        <v>192</v>
+      </c>
+      <c r="C86" s="8">
         <v>46226</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="8">
         <v>46239</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86" s="8">
         <v>46202</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="8">
         <v>46213</v>
       </c>
       <c r="G86">
@@ -3607,24 +3593,24 @@
       <c r="I86">
         <v>10</v>
       </c>
-      <c r="J86" s="5">
+      <c r="J86" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>201</v>
-      </c>
-      <c r="C87" t="s">
-        <v>102</v>
-      </c>
-      <c r="D87" s="2">
+        <v>193</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D87" s="8">
         <v>46315</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E87" s="8">
         <v>46097</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="8">
         <v>46289</v>
       </c>
       <c r="G87">
@@ -3639,18 +3625,18 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>202</v>
-      </c>
-      <c r="C88" t="s">
-        <v>102</v>
-      </c>
-      <c r="D88" s="2">
+        <v>194</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D88" s="8">
         <v>46232</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E88" s="8">
         <v>46097</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="8">
         <v>46206</v>
       </c>
       <c r="G88">
@@ -3665,21 +3651,21 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B89" t="s">
-        <v>204</v>
-      </c>
-      <c r="C89" t="s">
-        <v>102</v>
-      </c>
-      <c r="D89" t="s">
-        <v>57</v>
-      </c>
-      <c r="E89" s="2">
+        <v>196</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E89" s="8">
         <v>46097</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="8">
         <v>46101</v>
       </c>
       <c r="G89">
@@ -3688,27 +3674,27 @@
       <c r="I89">
         <v>0</v>
       </c>
-      <c r="J89" s="5">
+      <c r="J89" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B90" t="s">
-        <v>206</v>
-      </c>
-      <c r="C90" s="2">
+        <v>198</v>
+      </c>
+      <c r="C90" s="8">
         <v>46212</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="8">
         <v>46218</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="8">
         <v>46188</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="8">
         <v>46192</v>
       </c>
       <c r="G90">
@@ -3720,27 +3706,27 @@
       <c r="I90">
         <v>5</v>
       </c>
-      <c r="J90" s="5">
+      <c r="J90" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B91" t="s">
-        <v>208</v>
-      </c>
-      <c r="C91" s="2">
+        <v>200</v>
+      </c>
+      <c r="C91" s="8">
         <v>46219</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="8">
         <v>46232</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="8">
         <v>46195</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="8">
         <v>46206</v>
       </c>
       <c r="G91">
@@ -3752,24 +3738,24 @@
       <c r="I91">
         <v>10</v>
       </c>
-      <c r="J91" s="5">
+      <c r="J91" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>156</v>
-      </c>
-      <c r="C92" s="2">
+        <v>148</v>
+      </c>
+      <c r="C92" s="8">
         <v>46240</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="8">
         <v>46287</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E92" s="8">
         <v>46216</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="8">
         <v>46260</v>
       </c>
       <c r="G92">
@@ -3781,22 +3767,22 @@
       <c r="I92">
         <v>33</v>
       </c>
-      <c r="J92" s="5"/>
+      <c r="J92" s="4"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>209</v>
-      </c>
-      <c r="C93" s="2">
+        <v>201</v>
+      </c>
+      <c r="C93" s="8">
         <v>46240</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="8">
         <v>46282</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="8">
         <v>46216</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="8">
         <v>46255</v>
       </c>
       <c r="G93">
@@ -3808,25 +3794,25 @@
       <c r="I93">
         <v>30</v>
       </c>
-      <c r="J93" s="5"/>
+      <c r="J93" s="4"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B94" t="s">
-        <v>211</v>
-      </c>
-      <c r="C94" s="2">
+        <v>203</v>
+      </c>
+      <c r="C94" s="8">
         <v>46240</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94" s="8">
         <v>46253</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E94" s="8">
         <v>46216</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="8">
         <v>46227</v>
       </c>
       <c r="G94">
@@ -3838,27 +3824,27 @@
       <c r="I94">
         <v>10</v>
       </c>
-      <c r="J94" s="5">
+      <c r="J94" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B95" t="s">
-        <v>213</v>
-      </c>
-      <c r="C95" s="2">
+        <v>205</v>
+      </c>
+      <c r="C95" s="8">
         <v>46254</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="8">
         <v>46260</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E95" s="8">
         <v>46230</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="8">
         <v>46234</v>
       </c>
       <c r="G95">
@@ -3870,27 +3856,27 @@
       <c r="I95">
         <v>5</v>
       </c>
-      <c r="J95" s="5">
+      <c r="J95" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B96" t="s">
-        <v>215</v>
-      </c>
-      <c r="C96" s="2">
+        <v>207</v>
+      </c>
+      <c r="C96" s="8">
         <v>46261</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96" s="8">
         <v>46275</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="8">
         <v>46237</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="8">
         <v>46248</v>
       </c>
       <c r="G96">
@@ -3902,27 +3888,27 @@
       <c r="I96">
         <v>10</v>
       </c>
-      <c r="J96" s="5">
+      <c r="J96" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B97" t="s">
-        <v>217</v>
-      </c>
-      <c r="C97" s="2">
+        <v>209</v>
+      </c>
+      <c r="C97" s="8">
         <v>46276</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="8">
         <v>46282</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="8">
         <v>46251</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="8">
         <v>46255</v>
       </c>
       <c r="G97">
@@ -3934,24 +3920,24 @@
       <c r="I97">
         <v>5</v>
       </c>
-      <c r="J97" s="5">
+      <c r="J97" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>218</v>
-      </c>
-      <c r="C98" s="2">
+        <v>210</v>
+      </c>
+      <c r="C98" s="8">
         <v>46240</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="8">
         <v>46262</v>
       </c>
-      <c r="E98" s="2">
+      <c r="E98" s="8">
         <v>46216</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="8">
         <v>46238</v>
       </c>
       <c r="G98">
@@ -3963,25 +3949,25 @@
       <c r="I98">
         <v>17</v>
       </c>
-      <c r="J98" s="5"/>
+      <c r="J98" s="4"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B99" t="s">
-        <v>220</v>
-      </c>
-      <c r="C99" s="2">
+        <v>212</v>
+      </c>
+      <c r="C99" s="8">
         <v>46240</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="8">
         <v>46248</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="8">
         <v>46216</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="8">
         <v>46224</v>
       </c>
       <c r="G99">
@@ -3993,27 +3979,27 @@
       <c r="I99">
         <v>7</v>
       </c>
-      <c r="J99" s="5">
+      <c r="J99" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B100" t="s">
-        <v>222</v>
-      </c>
-      <c r="C100" s="2">
+        <v>214</v>
+      </c>
+      <c r="C100" s="8">
         <v>46251</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100" s="8">
         <v>46255</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="8">
         <v>46225</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="8">
         <v>46231</v>
       </c>
       <c r="G100">
@@ -4025,27 +4011,27 @@
       <c r="I100">
         <v>5</v>
       </c>
-      <c r="J100" s="5">
+      <c r="J100" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B101" t="s">
-        <v>224</v>
-      </c>
-      <c r="C101" s="2">
+        <v>216</v>
+      </c>
+      <c r="C101" s="8">
         <v>46258</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="8">
         <v>46262</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E101" s="8">
         <v>46232</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="8">
         <v>46238</v>
       </c>
       <c r="G101">
@@ -4057,24 +4043,24 @@
       <c r="I101">
         <v>5</v>
       </c>
-      <c r="J101" s="5">
+      <c r="J101" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>225</v>
-      </c>
-      <c r="C102" s="2">
+        <v>217</v>
+      </c>
+      <c r="C102" s="8">
         <v>46266</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102" s="8">
         <v>46286</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="8">
         <v>46239</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="8">
         <v>46259</v>
       </c>
       <c r="G102">
@@ -4086,25 +4072,25 @@
       <c r="I102">
         <v>15</v>
       </c>
-      <c r="J102" s="5"/>
+      <c r="J102" s="4"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>227</v>
-      </c>
-      <c r="C103" s="2">
+        <v>219</v>
+      </c>
+      <c r="C103" s="8">
         <v>46266</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="8">
         <v>46272</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="8">
         <v>46239</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="8">
         <v>46245</v>
       </c>
       <c r="G103">
@@ -4116,27 +4102,27 @@
       <c r="I103">
         <v>5</v>
       </c>
-      <c r="J103" s="5">
+      <c r="J103" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B104" t="s">
-        <v>229</v>
-      </c>
-      <c r="C104" s="2">
+        <v>221</v>
+      </c>
+      <c r="C104" s="8">
         <v>46273</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104" s="8">
         <v>46279</v>
       </c>
-      <c r="E104" s="2">
+      <c r="E104" s="8">
         <v>46246</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="8">
         <v>46252</v>
       </c>
       <c r="G104">
@@ -4148,27 +4134,27 @@
       <c r="I104">
         <v>5</v>
       </c>
-      <c r="J104" s="5">
+      <c r="J104" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B105" t="s">
-        <v>231</v>
-      </c>
-      <c r="C105" s="2">
+        <v>223</v>
+      </c>
+      <c r="C105" s="8">
         <v>46280</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="8">
         <v>46286</v>
       </c>
-      <c r="E105" s="2">
+      <c r="E105" s="8">
         <v>46253</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="8">
         <v>46259</v>
       </c>
       <c r="G105">
@@ -4180,24 +4166,24 @@
       <c r="I105">
         <v>5</v>
       </c>
-      <c r="J105" s="5">
+      <c r="J105" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>232</v>
-      </c>
-      <c r="C106" s="2">
+        <v>224</v>
+      </c>
+      <c r="C106" s="8">
         <v>46240</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106" s="8">
         <v>46246</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E106" s="8">
         <v>46216</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="8">
         <v>46220</v>
       </c>
       <c r="G106">
@@ -4209,25 +4195,25 @@
       <c r="I106">
         <v>5</v>
       </c>
-      <c r="J106" s="5"/>
+      <c r="J106" s="4"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B107" t="s">
-        <v>234</v>
-      </c>
-      <c r="C107" s="2">
+        <v>226</v>
+      </c>
+      <c r="C107" s="8">
         <v>46240</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="8">
         <v>46246</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="8">
         <v>46216</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="8">
         <v>46220</v>
       </c>
       <c r="G107">
@@ -4239,24 +4225,24 @@
       <c r="I107">
         <v>5</v>
       </c>
-      <c r="J107" s="5">
+      <c r="J107" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>235</v>
-      </c>
-      <c r="C108" s="2">
+        <v>227</v>
+      </c>
+      <c r="C108" s="8">
         <v>46283</v>
       </c>
-      <c r="D108" s="2">
+      <c r="D108" s="8">
         <v>46287</v>
       </c>
-      <c r="E108" s="2">
+      <c r="E108" s="8">
         <v>46258</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="8">
         <v>46260</v>
       </c>
       <c r="G108">
@@ -4268,25 +4254,25 @@
       <c r="I108">
         <v>3</v>
       </c>
-      <c r="J108" s="5"/>
+      <c r="J108" s="4"/>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B109" t="s">
-        <v>237</v>
-      </c>
-      <c r="C109" s="2">
+        <v>229</v>
+      </c>
+      <c r="C109" s="8">
         <v>46283</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D109" s="8">
         <v>46287</v>
       </c>
-      <c r="E109" s="2">
+      <c r="E109" s="8">
         <v>46258</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="8">
         <v>46260</v>
       </c>
       <c r="G109">
@@ -4298,24 +4284,24 @@
       <c r="I109">
         <v>3</v>
       </c>
-      <c r="J109" s="5">
+      <c r="J109" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>238</v>
-      </c>
-      <c r="C110" s="2">
+        <v>230</v>
+      </c>
+      <c r="C110" s="8">
         <v>46261</v>
       </c>
-      <c r="D110" s="2">
+      <c r="D110" s="8">
         <v>46268</v>
       </c>
-      <c r="E110" s="2">
+      <c r="E110" s="8">
         <v>46237</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="8">
         <v>46241</v>
       </c>
       <c r="G110">
@@ -4327,25 +4313,25 @@
       <c r="I110">
         <v>5</v>
       </c>
-      <c r="J110" s="5"/>
+      <c r="J110" s="4"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B111" t="s">
-        <v>240</v>
-      </c>
-      <c r="C111" s="2">
+        <v>232</v>
+      </c>
+      <c r="C111" s="8">
         <v>46261</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="8">
         <v>46268</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E111" s="8">
         <v>46237</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="8">
         <v>46241</v>
       </c>
       <c r="G111">
@@ -4357,24 +4343,24 @@
       <c r="I111">
         <v>5</v>
       </c>
-      <c r="J111" s="5">
+      <c r="J111" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>188</v>
-      </c>
-      <c r="C112" s="2">
+        <v>180</v>
+      </c>
+      <c r="C112" s="8">
         <v>46210</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112" s="8">
         <v>46219</v>
       </c>
-      <c r="E112" s="2">
+      <c r="E112" s="8">
         <v>46174</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="8">
         <v>46183</v>
       </c>
       <c r="G112">
@@ -4389,21 +4375,21 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B113" t="s">
-        <v>242</v>
-      </c>
-      <c r="C113" s="2">
+        <v>234</v>
+      </c>
+      <c r="C113" s="8">
         <v>46210</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="8">
         <v>46210</v>
       </c>
-      <c r="E113" s="2">
+      <c r="E113" s="8">
         <v>46174</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="8">
         <v>46174</v>
       </c>
       <c r="G113">
@@ -4415,27 +4401,27 @@
       <c r="I113">
         <v>0</v>
       </c>
-      <c r="J113" s="5">
+      <c r="J113" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B114" t="s">
-        <v>244</v>
-      </c>
-      <c r="C114" s="2">
+        <v>236</v>
+      </c>
+      <c r="C114" s="8">
         <v>46210</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114" s="8">
         <v>46219</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="8">
         <v>46174</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="8">
         <v>46183</v>
       </c>
       <c r="G114">
@@ -4447,24 +4433,24 @@
       <c r="I114">
         <v>8</v>
       </c>
-      <c r="J114" s="5">
+      <c r="J114" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>175</v>
-      </c>
-      <c r="C115" s="2">
+        <v>167</v>
+      </c>
+      <c r="C115" s="8">
         <v>46240</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="8">
         <v>46272</v>
       </c>
-      <c r="E115" s="2">
+      <c r="E115" s="8">
         <v>46216</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="8">
         <v>46245</v>
       </c>
       <c r="G115">
@@ -4476,22 +4462,22 @@
       <c r="I115">
         <v>22</v>
       </c>
-      <c r="J115" s="5"/>
+      <c r="J115" s="4"/>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>245</v>
-      </c>
-      <c r="C116" s="2">
+        <v>237</v>
+      </c>
+      <c r="C116" s="8">
         <v>46240</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="8">
         <v>46268</v>
       </c>
-      <c r="E116" s="2">
+      <c r="E116" s="8">
         <v>46216</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="8">
         <v>46241</v>
       </c>
       <c r="G116">
@@ -4503,25 +4489,25 @@
       <c r="I116">
         <v>20</v>
       </c>
-      <c r="J116" s="5"/>
+      <c r="J116" s="4"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B117" t="s">
-        <v>247</v>
-      </c>
-      <c r="C117" s="2">
+        <v>239</v>
+      </c>
+      <c r="C117" s="8">
         <v>46240</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="8">
         <v>46253</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E117" s="8">
         <v>46216</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="8">
         <v>46227</v>
       </c>
       <c r="G117">
@@ -4533,27 +4519,27 @@
       <c r="I117">
         <v>10</v>
       </c>
-      <c r="J117" s="5">
+      <c r="J117" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B118" t="s">
-        <v>249</v>
-      </c>
-      <c r="C118" s="2">
+        <v>241</v>
+      </c>
+      <c r="C118" s="8">
         <v>46261</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D118" s="8">
         <v>46268</v>
       </c>
-      <c r="E118" s="2">
+      <c r="E118" s="8">
         <v>46237</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="8">
         <v>46241</v>
       </c>
       <c r="G118">
@@ -4565,27 +4551,27 @@
       <c r="I118">
         <v>5</v>
       </c>
-      <c r="J118" s="5">
+      <c r="J118" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B119" t="s">
-        <v>251</v>
-      </c>
-      <c r="C119" s="2">
+        <v>243</v>
+      </c>
+      <c r="C119" s="8">
         <v>46261</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="8">
         <v>46268</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="8">
         <v>46237</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="8">
         <v>46241</v>
       </c>
       <c r="G119">
@@ -4597,24 +4583,24 @@
       <c r="I119">
         <v>5</v>
       </c>
-      <c r="J119" s="5">
+      <c r="J119" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>252</v>
-      </c>
-      <c r="C120" s="2">
+        <v>244</v>
+      </c>
+      <c r="C120" s="8">
         <v>46240</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120" s="8">
         <v>46272</v>
       </c>
-      <c r="E120" s="2">
+      <c r="E120" s="8">
         <v>46216</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="8">
         <v>46245</v>
       </c>
       <c r="G120">
@@ -4626,25 +4612,25 @@
       <c r="I120">
         <v>22</v>
       </c>
-      <c r="J120" s="5"/>
+      <c r="J120" s="4"/>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B121" t="s">
-        <v>254</v>
-      </c>
-      <c r="C121" s="2">
+        <v>246</v>
+      </c>
+      <c r="C121" s="8">
         <v>46240</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="8">
         <v>46244</v>
       </c>
-      <c r="E121" s="2">
+      <c r="E121" s="8">
         <v>46216</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="8">
         <v>46218</v>
       </c>
       <c r="G121">
@@ -4656,27 +4642,27 @@
       <c r="I121">
         <v>3</v>
       </c>
-      <c r="J121" s="5">
+      <c r="J121" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B122" t="s">
-        <v>256</v>
-      </c>
-      <c r="C122" s="2">
+        <v>248</v>
+      </c>
+      <c r="C122" s="8">
         <v>46245</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122" s="8">
         <v>46247</v>
       </c>
-      <c r="E122" s="2">
+      <c r="E122" s="8">
         <v>46219</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="8">
         <v>46223</v>
       </c>
       <c r="G122">
@@ -4688,27 +4674,27 @@
       <c r="I122">
         <v>3</v>
       </c>
-      <c r="J122" s="5">
+      <c r="J122" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B123" t="s">
-        <v>258</v>
-      </c>
-      <c r="C123" s="2">
+        <v>250</v>
+      </c>
+      <c r="C123" s="8">
         <v>46248</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="8">
         <v>46252</v>
       </c>
-      <c r="E123" s="2">
+      <c r="E123" s="8">
         <v>46224</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="8">
         <v>46226</v>
       </c>
       <c r="G123">
@@ -4720,27 +4706,27 @@
       <c r="I123">
         <v>3</v>
       </c>
-      <c r="J123" s="5">
+      <c r="J123" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B124" t="s">
-        <v>260</v>
-      </c>
-      <c r="C124" s="2">
+        <v>252</v>
+      </c>
+      <c r="C124" s="8">
         <v>46253</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="8">
         <v>46255</v>
       </c>
-      <c r="E124" s="2">
+      <c r="E124" s="8">
         <v>46227</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="8">
         <v>46231</v>
       </c>
       <c r="G124">
@@ -4752,27 +4738,27 @@
       <c r="I124">
         <v>3</v>
       </c>
-      <c r="J124" s="5">
+      <c r="J124" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B125" t="s">
-        <v>262</v>
-      </c>
-      <c r="C125" s="2">
+        <v>254</v>
+      </c>
+      <c r="C125" s="8">
         <v>46258</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="8">
         <v>46272</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="8">
         <v>46232</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="8">
         <v>46245</v>
       </c>
       <c r="G125">
@@ -4784,27 +4770,27 @@
       <c r="I125">
         <v>10</v>
       </c>
-      <c r="J125" s="5">
+      <c r="J125" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B126" t="s">
-        <v>264</v>
-      </c>
-      <c r="C126" s="2">
+        <v>256</v>
+      </c>
+      <c r="C126" s="8">
         <v>46258</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126" s="8">
         <v>46260</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="8">
         <v>46232</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="8">
         <v>46234</v>
       </c>
       <c r="G126">
@@ -4816,24 +4802,24 @@
       <c r="I126">
         <v>3</v>
       </c>
-      <c r="J126" s="5">
+      <c r="J126" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>265</v>
-      </c>
-      <c r="C127" t="s">
-        <v>266</v>
-      </c>
-      <c r="D127" s="2">
+        <v>257</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D127" s="8">
         <v>46233</v>
       </c>
-      <c r="E127" s="2">
+      <c r="E127" s="8">
         <v>46156</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="8">
         <v>46205</v>
       </c>
       <c r="G127">
@@ -4848,18 +4834,18 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>245</v>
-      </c>
-      <c r="C128" t="s">
-        <v>266</v>
-      </c>
-      <c r="D128" s="2">
+        <v>237</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D128" s="8">
         <v>46224</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="8">
         <v>46156</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="8">
         <v>46205</v>
       </c>
       <c r="G128">
@@ -4874,15 +4860,15 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B129" t="s">
-        <v>268</v>
-      </c>
-      <c r="C129" t="s">
-        <v>266</v>
-      </c>
-      <c r="E129" s="2">
+        <v>260</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E129" s="8">
         <v>46156</v>
       </c>
       <c r="G129">
@@ -4891,27 +4877,27 @@
       <c r="I129">
         <v>0</v>
       </c>
-      <c r="J129" s="5">
+      <c r="J129" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B130" t="s">
-        <v>270</v>
-      </c>
-      <c r="C130" t="s">
-        <v>271</v>
-      </c>
-      <c r="D130" s="2">
+        <v>262</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D130" s="8">
         <v>46209</v>
       </c>
-      <c r="E130" s="2">
+      <c r="E130" s="8">
         <v>46160</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="8">
         <v>46168</v>
       </c>
       <c r="G130">
@@ -4923,27 +4909,27 @@
       <c r="I130">
         <v>4</v>
       </c>
-      <c r="J130" s="5">
+      <c r="J130" s="4">
         <v>60</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B131" t="s">
-        <v>273</v>
-      </c>
-      <c r="C131" t="s">
-        <v>274</v>
-      </c>
-      <c r="D131" t="s">
-        <v>275</v>
-      </c>
-      <c r="E131" s="2">
+        <v>265</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E131" s="8">
         <v>46168</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="8">
         <v>46170</v>
       </c>
       <c r="G131">
@@ -4952,27 +4938,27 @@
       <c r="I131">
         <v>0</v>
       </c>
-      <c r="J131" s="5">
+      <c r="J131" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B132" t="s">
-        <v>277</v>
-      </c>
-      <c r="C132" t="s">
-        <v>278</v>
-      </c>
-      <c r="D132" t="s">
-        <v>72</v>
-      </c>
-      <c r="E132" s="2">
+        <v>269</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E132" s="8">
         <v>46171</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="8">
         <v>46184</v>
       </c>
       <c r="G132">
@@ -4981,27 +4967,27 @@
       <c r="I132">
         <v>0</v>
       </c>
-      <c r="J132" s="5">
+      <c r="J132" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B133" t="s">
-        <v>280</v>
-      </c>
-      <c r="C133" s="2">
+        <v>272</v>
+      </c>
+      <c r="C133" s="8">
         <v>46204</v>
       </c>
-      <c r="D133" s="2">
+      <c r="D133" s="8">
         <v>46217</v>
       </c>
-      <c r="E133" s="2">
+      <c r="E133" s="8">
         <v>46185</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="8">
         <v>46198</v>
       </c>
       <c r="G133">
@@ -5013,27 +4999,27 @@
       <c r="I133">
         <v>10</v>
       </c>
-      <c r="J133" s="5">
+      <c r="J133" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B134" t="s">
-        <v>282</v>
-      </c>
-      <c r="C134" s="2">
+        <v>274</v>
+      </c>
+      <c r="C134" s="8">
         <v>46210</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="8">
         <v>46216</v>
       </c>
-      <c r="E134" s="2">
+      <c r="E134" s="8">
         <v>46169</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="8">
         <v>46175</v>
       </c>
       <c r="G134">
@@ -5045,27 +5031,27 @@
       <c r="I134">
         <v>5</v>
       </c>
-      <c r="J134" s="5">
+      <c r="J134" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B135" t="s">
-        <v>284</v>
-      </c>
-      <c r="C135" s="2">
+        <v>276</v>
+      </c>
+      <c r="C135" s="8">
         <v>46217</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="8">
         <v>46219</v>
       </c>
-      <c r="E135" s="2">
+      <c r="E135" s="8">
         <v>46176</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="8">
         <v>46178</v>
       </c>
       <c r="G135">
@@ -5077,27 +5063,27 @@
       <c r="I135">
         <v>3</v>
       </c>
-      <c r="J135" s="5">
+      <c r="J135" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B136" t="s">
-        <v>286</v>
-      </c>
-      <c r="C136" s="2">
+        <v>278</v>
+      </c>
+      <c r="C136" s="8">
         <v>46218</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136" s="8">
         <v>46224</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="8">
         <v>46199</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="8">
         <v>46205</v>
       </c>
       <c r="G136">
@@ -5109,24 +5095,24 @@
       <c r="I136">
         <v>5</v>
       </c>
-      <c r="J136" s="5">
+      <c r="J136" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>252</v>
-      </c>
-      <c r="C137" t="s">
-        <v>278</v>
-      </c>
-      <c r="D137" s="2">
+        <v>244</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D137" s="8">
         <v>46233</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E137" s="8">
         <v>46171</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="8">
         <v>46192</v>
       </c>
       <c r="G137">
@@ -5141,21 +5127,21 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B138" t="s">
-        <v>288</v>
-      </c>
-      <c r="C138" t="s">
-        <v>278</v>
-      </c>
-      <c r="D138" s="2">
+        <v>280</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D138" s="8">
         <v>46209</v>
       </c>
-      <c r="E138" s="2">
+      <c r="E138" s="8">
         <v>46171</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="8">
         <v>46177</v>
       </c>
       <c r="G138">
@@ -5167,27 +5153,27 @@
       <c r="I138">
         <v>4</v>
       </c>
-      <c r="J138" s="5">
+      <c r="J138" s="4">
         <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B139" t="s">
-        <v>290</v>
-      </c>
-      <c r="C139" s="2">
+        <v>282</v>
+      </c>
+      <c r="C139" s="8">
         <v>46220</v>
       </c>
-      <c r="D139" s="2">
+      <c r="D139" s="8">
         <v>46226</v>
       </c>
-      <c r="E139" s="2">
+      <c r="E139" s="8">
         <v>46181</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="8">
         <v>46185</v>
       </c>
       <c r="G139">
@@ -5199,27 +5185,27 @@
       <c r="I139">
         <v>5</v>
       </c>
-      <c r="J139" s="5">
+      <c r="J139" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B140" t="s">
-        <v>292</v>
-      </c>
-      <c r="C140" s="2">
+        <v>284</v>
+      </c>
+      <c r="C140" s="8">
         <v>46227</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140" s="8">
         <v>46233</v>
       </c>
-      <c r="E140" s="2">
+      <c r="E140" s="8">
         <v>46188</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="8">
         <v>46192</v>
       </c>
       <c r="G140">
@@ -5231,24 +5217,24 @@
       <c r="I140">
         <v>5</v>
       </c>
-      <c r="J140" s="5">
+      <c r="J140" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>293</v>
-      </c>
-      <c r="C141" s="2">
+        <v>285</v>
+      </c>
+      <c r="C141" s="8">
         <v>46288</v>
       </c>
-      <c r="D141" s="2">
+      <c r="D141" s="8">
         <v>46315</v>
       </c>
-      <c r="E141" s="2">
+      <c r="E141" s="8">
         <v>46261</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="8">
         <v>46289</v>
       </c>
       <c r="G141">
@@ -5263,15 +5249,15 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B142" t="s">
-        <v>198</v>
-      </c>
-      <c r="C142" s="2">
+        <v>190</v>
+      </c>
+      <c r="C142" s="8">
         <v>46288</v>
       </c>
-      <c r="E142" s="2">
+      <c r="E142" s="8">
         <v>46261</v>
       </c>
       <c r="G142">
@@ -5283,27 +5269,27 @@
       <c r="I142">
         <v>0</v>
       </c>
-      <c r="J142" s="5">
+      <c r="J142" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B143" t="s">
-        <v>200</v>
-      </c>
-      <c r="C143" s="2">
+        <v>192</v>
+      </c>
+      <c r="C143" s="8">
         <v>46288</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="8">
         <v>46301</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="8">
         <v>46261</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="8">
         <v>46275</v>
       </c>
       <c r="G143">
@@ -5315,27 +5301,27 @@
       <c r="I143">
         <v>10</v>
       </c>
-      <c r="J143" s="5">
+      <c r="J143" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B144" t="s">
-        <v>297</v>
-      </c>
-      <c r="C144" s="2">
+        <v>289</v>
+      </c>
+      <c r="C144" s="8">
         <v>46302</v>
       </c>
-      <c r="D144" s="2">
+      <c r="D144" s="8">
         <v>46315</v>
       </c>
-      <c r="E144" s="2">
+      <c r="E144" s="8">
         <v>46276</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="8">
         <v>46289</v>
       </c>
       <c r="G144">
@@ -5347,21 +5333,21 @@
       <c r="I144">
         <v>10</v>
       </c>
-      <c r="J144" s="5">
+      <c r="J144" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B145" t="s">
-        <v>299</v>
-      </c>
-      <c r="D145" s="2">
+        <v>291</v>
+      </c>
+      <c r="D145" s="8">
         <v>46315</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="8">
         <v>46289</v>
       </c>
       <c r="G145">
@@ -5373,24 +5359,24 @@
       <c r="I145">
         <v>0</v>
       </c>
-      <c r="J145" s="5">
+      <c r="J145" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>300</v>
-      </c>
-      <c r="C146" t="s">
-        <v>52</v>
-      </c>
-      <c r="D146" t="s">
-        <v>57</v>
-      </c>
-      <c r="E146" s="2">
+        <v>292</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E146" s="8">
         <v>46094</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="8">
         <v>46101</v>
       </c>
       <c r="G146">
@@ -5402,15 +5388,15 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B147" t="s">
-        <v>302</v>
-      </c>
-      <c r="C147" t="s">
-        <v>52</v>
-      </c>
-      <c r="E147" s="2">
+        <v>294</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E147" s="8">
         <v>46094</v>
       </c>
       <c r="G147">
@@ -5419,21 +5405,21 @@
       <c r="I147">
         <v>0</v>
       </c>
-      <c r="J147" s="5">
+      <c r="J147" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B148" t="s">
-        <v>304</v>
-      </c>
-      <c r="C148" t="s">
-        <v>57</v>
-      </c>
-      <c r="E148" s="2">
+        <v>296</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E148" s="8">
         <v>46101</v>
       </c>
       <c r="G148">
@@ -5442,7 +5428,7 @@
       <c r="I148">
         <v>0</v>
       </c>
-      <c r="J148" s="6">
+      <c r="J148" s="5">
         <v>100</v>
       </c>
     </row>

--- a/data/Ferry/CL32-June-2026.xlsx
+++ b/data/Ferry/CL32-June-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Ferry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C7E579-B375-415A-A0CE-822E409C62AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A413ABB1-235B-4A71-9E65-CB9FF11D4855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C5AC1E55-1BE4-439D-8AD9-7FF9B9368B4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="266">
   <si>
     <t>Activity ID</t>
   </si>
@@ -131,9 +131,6 @@
     <t xml:space="preserve">  PMI's/EWN's/CE's</t>
   </si>
   <si>
-    <t>10-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-CHA-1010</t>
   </si>
   <si>
@@ -185,9 +182,6 @@
     <t>[GET] - Maximum flowrate in overflow pipe</t>
   </si>
   <si>
-    <t>13-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-DEP-1050</t>
   </si>
   <si>
@@ -200,9 +194,6 @@
     <t>[GET] - Manhole records/cards</t>
   </si>
   <si>
-    <t>20-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-DEP-1080</t>
   </si>
   <si>
@@ -242,9 +233,6 @@
     <t xml:space="preserve">    TQ's / RFI's</t>
   </si>
   <si>
-    <t>11-Jun-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-DEP-1140</t>
   </si>
   <si>
@@ -287,36 +275,24 @@
     <t xml:space="preserve">  Mobilisation</t>
   </si>
   <si>
-    <t>27-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-MOB-1000</t>
   </si>
   <si>
     <t>Mobilisation</t>
   </si>
   <si>
-    <t>20-Feb-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-MOB-1010</t>
   </si>
   <si>
     <t>Review Information and raise RFI/TQs</t>
   </si>
   <si>
-    <t>27-Feb-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-MOB-1020</t>
   </si>
   <si>
     <t>Meeting with Murphy &amp; UU - Confirmation of revised scope received</t>
   </si>
   <si>
-    <t>09-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-MOB-1030</t>
   </si>
   <si>
@@ -329,18 +305,12 @@
     <t>Murphy Response to TQs</t>
   </si>
   <si>
-    <t>16-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Deliverables</t>
   </si>
   <si>
     <t xml:space="preserve">    JMS001-PS-RFQ-000001 - Optioneering Assessment</t>
   </si>
   <si>
-    <t>13-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-CHA-1030</t>
   </si>
   <si>
@@ -377,12 +347,6 @@
     <t>Civil Modelling - Tank</t>
   </si>
   <si>
-    <t>24-Apr-26 A</t>
-  </si>
-  <si>
-    <t>30-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-3D-1060</t>
   </si>
   <si>
@@ -401,9 +365,6 @@
     <t>Network modelling (to be done by Arup)</t>
   </si>
   <si>
-    <t>16-Jun-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-3D-1010</t>
   </si>
   <si>
@@ -419,9 +380,6 @@
     <t>Determine entry/exit levels for pipework to and from overflow pipe</t>
   </si>
   <si>
-    <t>02-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-CSD-1010</t>
   </si>
   <si>
@@ -446,9 +404,6 @@
     <t>[GET] - MGE to provide initial guidance on pile size and spacing</t>
   </si>
   <si>
-    <t>24-Jun-26 A</t>
-  </si>
-  <si>
     <t>5 Day lag from when Network modelling completed</t>
   </si>
   <si>
@@ -458,9 +413,6 @@
     <t>Check on shaft sizing and buoyancy assessment</t>
   </si>
   <si>
-    <t>25-Jun-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-CSD-1060</t>
   </si>
   <si>
@@ -482,9 +434,6 @@
     <t xml:space="preserve">    Outline Design Scope Freeze (Minimum Requirements)</t>
   </si>
   <si>
-    <t>23-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      Civils Design</t>
   </si>
   <si>
@@ -500,36 +449,18 @@
     <t>Outline drawing for connection into existing manhole on inlet pipe</t>
   </si>
   <si>
-    <t>07-Apr-26 A</t>
-  </si>
-  <si>
-    <t>13-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1020</t>
   </si>
   <si>
     <t>GA &amp; Long sections of pipe entry/exit pipework from new MHs</t>
   </si>
   <si>
-    <t>14-Apr-26 A</t>
-  </si>
-  <si>
-    <t>20-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1030</t>
   </si>
   <si>
     <t>Valve chamber standard detail drawing showing dimensions and layout</t>
   </si>
   <si>
-    <t>21-Apr-26 A</t>
-  </si>
-  <si>
-    <t>22-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1040</t>
   </si>
   <si>
@@ -563,9 +494,6 @@
     <t>Pump system curve and calcs with pump selection</t>
   </si>
   <si>
-    <t>27-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-MEC-1120</t>
   </si>
   <si>
@@ -578,9 +506,6 @@
     <t>[GET] response to JMS-MAE-TQ-000044</t>
   </si>
   <si>
-    <t>12-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      Process Design</t>
   </si>
   <si>
@@ -590,9 +515,6 @@
     <t>Basis of Design</t>
   </si>
   <si>
-    <t>17-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-PRO-1000</t>
   </si>
   <si>
@@ -815,9 +737,6 @@
     <t xml:space="preserve">      EICA Design</t>
   </si>
   <si>
-    <t>14-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-EICA-1100</t>
   </si>
   <si>
@@ -830,28 +749,16 @@
     <t>User Requirement Specification</t>
   </si>
   <si>
-    <t>18-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-EICA-1020</t>
   </si>
   <si>
     <t>Load Schedule</t>
   </si>
   <si>
-    <t>26-May-26 A</t>
-  </si>
-  <si>
-    <t>28-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-EICA-1040</t>
   </si>
   <si>
     <t>Power Supply Assessment</t>
-  </si>
-  <si>
-    <t>29-May-26 A</t>
   </si>
   <si>
     <t xml:space="preserve">          FER-EICA-1050</t>
@@ -1691,10 +1598,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
       </c>
       <c r="C14" s="8">
         <v>46122</v>
@@ -1714,19 +1621,19 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
         <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
       </c>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
         <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
       </c>
       <c r="D16" s="8">
         <v>46135</v>
@@ -1744,10 +1651,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
         <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>38</v>
       </c>
       <c r="C17" s="8">
         <v>46153</v>
@@ -1767,7 +1674,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="8">
         <v>46069</v>
@@ -1794,10 +1701,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>41</v>
       </c>
       <c r="C19" s="8">
         <v>46069</v>
@@ -1817,10 +1724,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
         <v>42</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
       </c>
       <c r="C20" s="8">
         <v>46069</v>
@@ -1840,10 +1747,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
         <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>45</v>
       </c>
       <c r="C21" s="8">
         <v>46093</v>
@@ -1863,10 +1770,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
         <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
       </c>
       <c r="C22" s="8">
         <v>46094</v>
@@ -1886,10 +1793,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C23" s="8">
         <v>46094</v>
@@ -1909,10 +1816,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C24" s="8">
         <v>46101</v>
@@ -1932,10 +1839,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C25" s="8">
         <v>46101</v>
@@ -1955,10 +1862,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C26" s="8">
         <v>46101</v>
@@ -1978,10 +1885,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C27" s="8">
         <v>46101</v>
@@ -2001,10 +1908,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C28" s="8">
         <v>46101</v>
@@ -2024,10 +1931,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C29" s="8">
         <v>46101</v>
@@ -2047,10 +1954,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C30" s="8">
         <v>46204</v>
@@ -2073,7 +1980,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C31" s="8">
         <v>46184</v>
@@ -2090,10 +1997,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C32" s="8">
         <v>46184</v>
@@ -2107,10 +2014,10 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C33" s="8">
         <v>46184</v>
@@ -2124,10 +2031,10 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C34" s="8">
         <v>46184</v>
@@ -2141,10 +2048,10 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D35" s="8">
         <v>46204</v>
@@ -2159,15 +2066,15 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D36" s="8">
         <v>46204</v>
@@ -2182,15 +2089,15 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D37" s="8">
         <v>46204</v>
@@ -2205,18 +2112,18 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C38" s="8">
         <v>46069</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>82</v>
+      <c r="D38" s="8">
+        <v>46108</v>
       </c>
       <c r="E38" s="8">
         <v>46069</v>
@@ -2233,16 +2140,16 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C39" s="8">
         <v>46069</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>85</v>
+      <c r="D39" s="8">
+        <v>46073</v>
       </c>
       <c r="E39" s="8">
         <v>46069</v>
@@ -2262,16 +2169,16 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C40" s="8">
         <v>46076</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>88</v>
+      <c r="D40" s="8">
+        <v>46080</v>
       </c>
       <c r="E40" s="8">
         <v>46076</v>
@@ -2291,16 +2198,16 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C41" s="8">
         <v>46090</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>91</v>
+      <c r="D41" s="8">
+        <v>46090</v>
       </c>
       <c r="E41" s="8">
         <v>46090</v>
@@ -2320,16 +2227,16 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C42" s="8">
         <v>46090</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>48</v>
+      <c r="D42" s="8">
+        <v>46094</v>
       </c>
       <c r="E42" s="8">
         <v>46090</v>
@@ -2349,16 +2256,16 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C43" s="8">
         <v>46097</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>82</v>
+      <c r="D43" s="8">
+        <v>46108</v>
       </c>
       <c r="E43" s="8">
         <v>46097</v>
@@ -2378,7 +2285,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C44" s="8">
         <v>46097</v>
@@ -2404,13 +2311,13 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C45" s="8">
         <v>46141</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>99</v>
+      <c r="D45" s="8">
+        <v>46155</v>
       </c>
       <c r="E45" s="8">
         <v>46141</v>
@@ -2427,16 +2334,16 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C46" s="8">
         <v>46141</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>99</v>
+      <c r="D46" s="8">
+        <v>46155</v>
       </c>
       <c r="E46" s="8">
         <v>46141</v>
@@ -2456,7 +2363,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C47" s="8">
         <v>46111</v>
@@ -2482,16 +2389,16 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C48" s="8">
         <v>46111</v>
       </c>
-      <c r="D48" s="7" t="s">
-        <v>36</v>
+      <c r="D48" s="8">
+        <v>46135</v>
       </c>
       <c r="E48" s="8">
         <v>46111</v>
@@ -2511,16 +2418,16 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C49" s="8">
         <v>46111</v>
       </c>
-      <c r="D49" s="7" t="s">
-        <v>36</v>
+      <c r="D49" s="8">
+        <v>46135</v>
       </c>
       <c r="E49" s="8">
         <v>46111</v>
@@ -2540,16 +2447,16 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C50" s="8">
         <v>46122</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>36</v>
+      <c r="D50" s="8">
+        <v>46135</v>
       </c>
       <c r="E50" s="8">
         <v>46122</v>
@@ -2569,16 +2476,16 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C51" s="8">
         <v>46136</v>
       </c>
-      <c r="D51" s="7" t="s">
-        <v>113</v>
+      <c r="D51" s="8">
+        <v>46142</v>
       </c>
       <c r="E51" s="8">
         <v>46136</v>
@@ -2598,10 +2505,10 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C52" s="8">
         <v>46143</v>
@@ -2630,10 +2537,10 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B53" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C53" s="8">
         <v>46143</v>
@@ -2662,13 +2569,13 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B54" t="s">
-        <v>119</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>120</v>
+        <v>107</v>
+      </c>
+      <c r="D54" s="8">
+        <v>46189</v>
       </c>
       <c r="F54" s="8">
         <v>46163</v>
@@ -2683,15 +2590,15 @@
         <v>100</v>
       </c>
       <c r="K54" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C55" s="8">
         <v>46204</v>
@@ -2720,10 +2627,10 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D56" s="8">
         <v>46232</v>
@@ -2746,16 +2653,16 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B57" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>126</v>
+        <v>93</v>
+      </c>
+      <c r="D57" s="8">
+        <v>46114</v>
       </c>
       <c r="E57" s="8">
         <v>46111</v>
@@ -2775,16 +2682,16 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="B58" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>126</v>
+        <v>93</v>
+      </c>
+      <c r="D58" s="8">
+        <v>46114</v>
       </c>
       <c r="E58" s="8">
         <v>46111</v>
@@ -2804,16 +2711,16 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>126</v>
+        <v>93</v>
+      </c>
+      <c r="D59" s="8">
+        <v>46114</v>
       </c>
       <c r="E59" s="8">
         <v>46111</v>
@@ -2833,16 +2740,16 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>126</v>
+        <v>93</v>
+      </c>
+      <c r="D60" s="8">
+        <v>46114</v>
       </c>
       <c r="E60" s="8">
         <v>46111</v>
@@ -2862,13 +2769,13 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>135</v>
+        <v>120</v>
+      </c>
+      <c r="D61" s="8">
+        <v>46197</v>
       </c>
       <c r="F61" s="8">
         <v>46174</v>
@@ -2883,18 +2790,18 @@
         <v>100</v>
       </c>
       <c r="K61" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="B62" t="s">
-        <v>138</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>139</v>
+        <v>123</v>
+      </c>
+      <c r="C62" s="8">
+        <v>46198</v>
       </c>
       <c r="D62" s="8">
         <v>46204</v>
@@ -2920,10 +2827,10 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C63" s="8">
         <v>46205</v>
@@ -2952,10 +2859,10 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B64" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="C64" s="8">
         <v>46212</v>
@@ -2984,10 +2891,10 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B65" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="C65" s="8">
         <v>46226</v>
@@ -3016,10 +2923,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>146</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>147</v>
+        <v>130</v>
+      </c>
+      <c r="C66" s="8">
+        <v>46104</v>
       </c>
       <c r="D66" s="8">
         <v>46239</v>
@@ -3042,10 +2949,10 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>148</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>103</v>
+        <v>131</v>
+      </c>
+      <c r="C67" s="8">
+        <v>46111</v>
       </c>
       <c r="D67" s="8">
         <v>46225</v>
@@ -3068,16 +2975,16 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="B68" t="s">
-        <v>150</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
+      </c>
+      <c r="C68" s="8">
+        <v>46111</v>
+      </c>
+      <c r="D68" s="8">
+        <v>46114</v>
       </c>
       <c r="E68" s="8">
         <v>46111</v>
@@ -3097,16 +3004,16 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="B69" t="s">
-        <v>152</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>154</v>
+        <v>135</v>
+      </c>
+      <c r="C69" s="8">
+        <v>46119</v>
+      </c>
+      <c r="D69" s="8">
+        <v>46125</v>
       </c>
       <c r="E69" s="8">
         <v>46119</v>
@@ -3126,16 +3033,16 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="B70" t="s">
-        <v>156</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>158</v>
+        <v>137</v>
+      </c>
+      <c r="C70" s="8">
+        <v>46126</v>
+      </c>
+      <c r="D70" s="8">
+        <v>46132</v>
       </c>
       <c r="E70" s="8">
         <v>46126</v>
@@ -3155,16 +3062,16 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="B71" t="s">
-        <v>160</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>162</v>
+        <v>139</v>
+      </c>
+      <c r="C71" s="8">
+        <v>46133</v>
+      </c>
+      <c r="D71" s="8">
+        <v>46164</v>
       </c>
       <c r="E71" s="8">
         <v>46133</v>
@@ -3184,10 +3091,10 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="B72" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="C72" s="8">
         <v>46204</v>
@@ -3216,10 +3123,10 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="B73" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="C73" s="8">
         <v>46212</v>
@@ -3248,13 +3155,13 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>167</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>162</v>
+        <v>144</v>
+      </c>
+      <c r="C74" s="8">
+        <v>46111</v>
+      </c>
+      <c r="D74" s="8">
+        <v>46164</v>
       </c>
       <c r="E74" s="8">
         <v>46111</v>
@@ -3271,16 +3178,16 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>30</v>
+        <v>146</v>
+      </c>
+      <c r="C75" s="8">
+        <v>46111</v>
+      </c>
+      <c r="D75" s="8">
+        <v>46122</v>
       </c>
       <c r="E75" s="8">
         <v>46111</v>
@@ -3300,16 +3207,16 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>112</v>
+        <v>148</v>
+      </c>
+      <c r="C76" s="8">
+        <v>46125</v>
+      </c>
+      <c r="D76" s="8">
+        <v>46136</v>
       </c>
       <c r="E76" s="8">
         <v>46125</v>
@@ -3329,16 +3236,16 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="B77" t="s">
-        <v>173</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>162</v>
+        <v>150</v>
+      </c>
+      <c r="C77" s="8">
+        <v>46139</v>
+      </c>
+      <c r="D77" s="8">
+        <v>46164</v>
       </c>
       <c r="E77" s="8">
         <v>46139</v>
@@ -3358,13 +3265,13 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="B78" t="s">
-        <v>176</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>113</v>
+        <v>152</v>
+      </c>
+      <c r="C78" s="8">
+        <v>46142</v>
       </c>
       <c r="E78" s="8">
         <v>46142</v>
@@ -3381,13 +3288,13 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="B79" t="s">
-        <v>178</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>179</v>
+        <v>154</v>
+      </c>
+      <c r="D79" s="8">
+        <v>46154</v>
       </c>
       <c r="F79" s="8">
         <v>46154</v>
@@ -3404,13 +3311,13 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>180</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>112</v>
+        <v>155</v>
+      </c>
+      <c r="C80" s="8">
+        <v>46104</v>
+      </c>
+      <c r="D80" s="8">
+        <v>46136</v>
       </c>
       <c r="E80" s="8">
         <v>46104</v>
@@ -3428,16 +3335,16 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="B81" t="s">
-        <v>182</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>183</v>
+        <v>157</v>
+      </c>
+      <c r="C81" s="8">
+        <v>46104</v>
+      </c>
+      <c r="D81" s="8">
+        <v>46129</v>
       </c>
       <c r="E81" s="8">
         <v>46104</v>
@@ -3457,16 +3364,16 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="B82" t="s">
-        <v>185</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>183</v>
+        <v>159</v>
+      </c>
+      <c r="C82" s="8">
+        <v>46111</v>
+      </c>
+      <c r="D82" s="8">
+        <v>46129</v>
       </c>
       <c r="E82" s="8">
         <v>46111</v>
@@ -3486,16 +3393,16 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="B83" t="s">
-        <v>187</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>112</v>
+        <v>161</v>
+      </c>
+      <c r="C83" s="8">
+        <v>46132</v>
+      </c>
+      <c r="D83" s="8">
+        <v>46136</v>
       </c>
       <c r="E83" s="8">
         <v>46132</v>
@@ -3515,7 +3422,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="C84" s="8">
         <v>46226</v>
@@ -3541,10 +3448,10 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="C85" s="8">
         <v>46226</v>
@@ -3567,10 +3474,10 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="B86" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="C86" s="8">
         <v>46226</v>
@@ -3599,10 +3506,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>193</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>96</v>
+        <v>167</v>
+      </c>
+      <c r="C87" s="8">
+        <v>46097</v>
       </c>
       <c r="D87" s="8">
         <v>46315</v>
@@ -3625,10 +3532,10 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>194</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>96</v>
+        <v>168</v>
+      </c>
+      <c r="C88" s="8">
+        <v>46097</v>
       </c>
       <c r="D88" s="8">
         <v>46232</v>
@@ -3651,16 +3558,16 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="B89" t="s">
-        <v>196</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>53</v>
+        <v>170</v>
+      </c>
+      <c r="C89" s="8">
+        <v>46097</v>
+      </c>
+      <c r="D89" s="8">
+        <v>46101</v>
       </c>
       <c r="E89" s="8">
         <v>46097</v>
@@ -3680,10 +3587,10 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="B90" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="C90" s="8">
         <v>46212</v>
@@ -3712,10 +3619,10 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="B91" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="C91" s="8">
         <v>46219</v>
@@ -3744,7 +3651,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="C92" s="8">
         <v>46240</v>
@@ -3771,7 +3678,7 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="C93" s="8">
         <v>46240</v>
@@ -3798,10 +3705,10 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="B94" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="C94" s="8">
         <v>46240</v>
@@ -3830,10 +3737,10 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="B95" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="C95" s="8">
         <v>46254</v>
@@ -3862,10 +3769,10 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="B96" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="C96" s="8">
         <v>46261</v>
@@ -3894,10 +3801,10 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="B97" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="C97" s="8">
         <v>46276</v>
@@ -3926,7 +3833,7 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="C98" s="8">
         <v>46240</v>
@@ -3953,10 +3860,10 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="B99" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="C99" s="8">
         <v>46240</v>
@@ -3985,10 +3892,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="B100" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="C100" s="8">
         <v>46251</v>
@@ -4017,10 +3924,10 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="B101" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="C101" s="8">
         <v>46258</v>
@@ -4049,7 +3956,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="C102" s="8">
         <v>46266</v>
@@ -4076,10 +3983,10 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="B103" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="C103" s="8">
         <v>46266</v>
@@ -4108,10 +4015,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="B104" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="C104" s="8">
         <v>46273</v>
@@ -4140,10 +4047,10 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="B105" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="C105" s="8">
         <v>46280</v>
@@ -4172,7 +4079,7 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="C106" s="8">
         <v>46240</v>
@@ -4199,10 +4106,10 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="B107" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="C107" s="8">
         <v>46240</v>
@@ -4231,7 +4138,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="C108" s="8">
         <v>46283</v>
@@ -4258,10 +4165,10 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="B109" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="C109" s="8">
         <v>46283</v>
@@ -4290,7 +4197,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="C110" s="8">
         <v>46261</v>
@@ -4317,10 +4224,10 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="B111" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="C111" s="8">
         <v>46261</v>
@@ -4349,7 +4256,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="C112" s="8">
         <v>46210</v>
@@ -4375,10 +4282,10 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="B113" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="C113" s="8">
         <v>46210</v>
@@ -4407,10 +4314,10 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="B114" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="C114" s="8">
         <v>46210</v>
@@ -4439,7 +4346,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C115" s="8">
         <v>46240</v>
@@ -4466,7 +4373,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="C116" s="8">
         <v>46240</v>
@@ -4493,10 +4400,10 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="B117" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="C117" s="8">
         <v>46240</v>
@@ -4525,10 +4432,10 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B118" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="C118" s="8">
         <v>46261</v>
@@ -4557,10 +4464,10 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="B119" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="C119" s="8">
         <v>46261</v>
@@ -4589,7 +4496,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C120" s="8">
         <v>46240</v>
@@ -4616,10 +4523,10 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="B121" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="C121" s="8">
         <v>46240</v>
@@ -4648,10 +4555,10 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="B122" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="C122" s="8">
         <v>46245</v>
@@ -4680,10 +4587,10 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="B123" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="C123" s="8">
         <v>46248</v>
@@ -4712,10 +4619,10 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="B124" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="C124" s="8">
         <v>46253</v>
@@ -4744,10 +4651,10 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="B125" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="C125" s="8">
         <v>46258</v>
@@ -4776,10 +4683,10 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="B126" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="C126" s="8">
         <v>46258</v>
@@ -4808,10 +4715,10 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>257</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>258</v>
+        <v>231</v>
+      </c>
+      <c r="C127" s="8">
+        <v>46156</v>
       </c>
       <c r="D127" s="8">
         <v>46233</v>
@@ -4834,10 +4741,10 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>237</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>258</v>
+        <v>211</v>
+      </c>
+      <c r="C128" s="8">
+        <v>46156</v>
       </c>
       <c r="D128" s="8">
         <v>46224</v>
@@ -4860,13 +4767,13 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="B129" t="s">
-        <v>260</v>
-      </c>
-      <c r="C129" s="7" t="s">
-        <v>258</v>
+        <v>233</v>
+      </c>
+      <c r="C129" s="8">
+        <v>46156</v>
       </c>
       <c r="E129" s="8">
         <v>46156</v>
@@ -4883,13 +4790,13 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="B130" t="s">
-        <v>262</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>263</v>
+        <v>235</v>
+      </c>
+      <c r="C130" s="8">
+        <v>46160</v>
       </c>
       <c r="D130" s="8">
         <v>46209</v>
@@ -4915,16 +4822,16 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="B131" t="s">
-        <v>265</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>267</v>
+        <v>237</v>
+      </c>
+      <c r="C131" s="8">
+        <v>46168</v>
+      </c>
+      <c r="D131" s="8">
+        <v>46170</v>
       </c>
       <c r="E131" s="8">
         <v>46168</v>
@@ -4944,16 +4851,16 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
       <c r="B132" t="s">
-        <v>269</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>67</v>
+        <v>239</v>
+      </c>
+      <c r="C132" s="8">
+        <v>46171</v>
+      </c>
+      <c r="D132" s="8">
+        <v>46184</v>
       </c>
       <c r="E132" s="8">
         <v>46171</v>
@@ -4973,10 +4880,10 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="B133" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="C133" s="8">
         <v>46204</v>
@@ -5005,10 +4912,10 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="B134" t="s">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="C134" s="8">
         <v>46210</v>
@@ -5037,10 +4944,10 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>275</v>
+        <v>244</v>
       </c>
       <c r="B135" t="s">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="C135" s="8">
         <v>46217</v>
@@ -5069,10 +4976,10 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="B136" t="s">
-        <v>278</v>
+        <v>247</v>
       </c>
       <c r="C136" s="8">
         <v>46218</v>
@@ -5101,10 +5008,10 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>244</v>
-      </c>
-      <c r="C137" s="7" t="s">
-        <v>270</v>
+        <v>218</v>
+      </c>
+      <c r="C137" s="8">
+        <v>46171</v>
       </c>
       <c r="D137" s="8">
         <v>46233</v>
@@ -5127,13 +5034,13 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>279</v>
+        <v>248</v>
       </c>
       <c r="B138" t="s">
-        <v>280</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>270</v>
+        <v>249</v>
+      </c>
+      <c r="C138" s="8">
+        <v>46171</v>
       </c>
       <c r="D138" s="8">
         <v>46209</v>
@@ -5159,10 +5066,10 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>281</v>
+        <v>250</v>
       </c>
       <c r="B139" t="s">
-        <v>282</v>
+        <v>251</v>
       </c>
       <c r="C139" s="8">
         <v>46220</v>
@@ -5191,10 +5098,10 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="B140" t="s">
-        <v>284</v>
+        <v>253</v>
       </c>
       <c r="C140" s="8">
         <v>46227</v>
@@ -5223,7 +5130,7 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>285</v>
+        <v>254</v>
       </c>
       <c r="C141" s="8">
         <v>46288</v>
@@ -5249,10 +5156,10 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="B142" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="C142" s="8">
         <v>46288</v>
@@ -5275,10 +5182,10 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="B143" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="C143" s="8">
         <v>46288</v>
@@ -5307,10 +5214,10 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="B144" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="C144" s="8">
         <v>46302</v>
@@ -5339,10 +5246,10 @@
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>290</v>
+        <v>259</v>
       </c>
       <c r="B145" t="s">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="D145" s="8">
         <v>46315</v>
@@ -5365,13 +5272,13 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>292</v>
-      </c>
-      <c r="C146" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D146" s="7" t="s">
-        <v>53</v>
+        <v>261</v>
+      </c>
+      <c r="C146" s="8">
+        <v>46094</v>
+      </c>
+      <c r="D146" s="8">
+        <v>46101</v>
       </c>
       <c r="E146" s="8">
         <v>46094</v>
@@ -5388,13 +5295,13 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="B147" t="s">
-        <v>294</v>
-      </c>
-      <c r="C147" s="7" t="s">
-        <v>48</v>
+        <v>263</v>
+      </c>
+      <c r="C147" s="8">
+        <v>46094</v>
       </c>
       <c r="E147" s="8">
         <v>46094</v>
@@ -5411,13 +5318,13 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="B148" t="s">
-        <v>296</v>
-      </c>
-      <c r="C148" s="7" t="s">
-        <v>53</v>
+        <v>265</v>
+      </c>
+      <c r="C148" s="8">
+        <v>46101</v>
       </c>
       <c r="E148" s="8">
         <v>46101</v>

--- a/data/Ferry/CL32-June-2026.xlsx
+++ b/data/Ferry/CL32-June-2026.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1134B0-8D60-4E41-B73B-CDE48A63C274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C5AC1E55-1BE4-439D-8AD9-7FF9B9368B4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C5AC1E55-1BE4-439D-8AD9-7FF9B9368B4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/Ferry/CL32-June-2026.xlsx
+++ b/data/Ferry/CL32-June-2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1134B0-8D60-4E41-B73B-CDE48A63C274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C5AC1E55-1BE4-439D-8AD9-7FF9B9368B4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C5AC1E55-1BE4-439D-8AD9-7FF9B9368B4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
